--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC50E8B-DBDF-4854-88AC-0A09A8BAAD89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D58FE-CE6B-4ECD-9102-72CA24C5B84B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="899">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -2559,9 +2559,6 @@
     <t>Гідравлічні крани кульові високого тиску з внутрішнім конусом 60°</t>
   </si>
   <si>
-    <t>child1_14.jpg</t>
-  </si>
-  <si>
     <t>Кран запірний кульовий двоходовий з двома штуцерами з внутрішнім конусом 60° для гідравлічних систем (під сфероконічне ущільнення)</t>
   </si>
   <si>
@@ -3576,9 +3573,6 @@
 4. Матеріал быстроразъемной муфти — алюміній
 5. Розташування цангових виводів — пряме
 6. Виконання быстроразъемной муфти — євро тип (Euro-type)</t>
-  </si>
-  <si>
-    <t>Гідравлічні крани кульові високого тиску</t>
   </si>
   <si>
     <t>child3_small_175.jpg</t>
@@ -5315,10 +5309,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>731</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -5987,7 +5981,7 @@
         <v>148</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>149</v>
@@ -6019,7 +6013,7 @@
         <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>152</v>
@@ -6435,10 +6429,10 @@
         <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>210</v>
@@ -6467,10 +6461,10 @@
         <v>157</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>212</v>
@@ -6659,10 +6653,10 @@
         <v>218</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>239</v>
@@ -7197,7 +7191,7 @@
         <v>317</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>317</v>
@@ -7229,13 +7223,13 @@
         <v>317</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>318</v>
@@ -7261,13 +7255,13 @@
         <v>317</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>318</v>
@@ -7293,13 +7287,13 @@
         <v>317</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>323</v>
@@ -7325,13 +7319,13 @@
         <v>317</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>323</v>
@@ -7971,16 +7965,16 @@
         <v>328</v>
       </c>
       <c r="G98" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="H98" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="J98" t="s">
         <v>677</v>
-      </c>
-      <c r="J98" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -8003,16 +7997,16 @@
         <v>328</v>
       </c>
       <c r="G99" t="s">
+        <v>678</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="J99" t="s">
         <v>681</v>
-      </c>
-      <c r="J99" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8035,16 +8029,16 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H100" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="J100" t="s">
         <v>685</v>
-      </c>
-      <c r="J100" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8067,16 +8061,16 @@
         <v>328</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H101" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="J101" t="s">
         <v>688</v>
-      </c>
-      <c r="J101" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -8928,10 +8922,10 @@
         <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>516</v>
@@ -8960,10 +8954,10 @@
         <v>515</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>519</v>
@@ -8992,7 +8986,7 @@
         <v>515</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>522</v>
@@ -9012,31 +9006,31 @@
         <v>134</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>435</v>
+        <v>316</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>732</v>
+        <v>514</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>526</v>
       </c>
       <c r="G131" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="I131" s="1" t="s">
+      <c r="J131" t="s">
         <v>530</v>
-      </c>
-      <c r="J131" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -9044,31 +9038,31 @@
         <v>135</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>435</v>
+        <v>316</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>732</v>
+        <v>514</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>526</v>
       </c>
       <c r="G132" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="I132" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="I132" s="1" t="s">
+      <c r="J132" t="s">
         <v>534</v>
-      </c>
-      <c r="J132" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -9076,31 +9070,31 @@
         <v>137</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F133" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G133" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="I133" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J133" t="s">
         <v>542</v>
-      </c>
-      <c r="J133" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -9108,31 +9102,31 @@
         <v>138</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G134" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="I134" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J134" t="s">
         <v>545</v>
-      </c>
-      <c r="J134" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -9140,31 +9134,31 @@
         <v>139</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="F135" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G135" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="I135" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="J135" t="s">
         <v>548</v>
-      </c>
-      <c r="J135" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -9172,31 +9166,31 @@
         <v>140</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F136" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G136" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="I136" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="I136" s="1" t="s">
+      <c r="J136" t="s">
         <v>552</v>
-      </c>
-      <c r="J136" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -9204,31 +9198,31 @@
         <v>141</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="F137" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F137" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G137" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="I137" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="I137" s="1" t="s">
+      <c r="J137" t="s">
         <v>556</v>
-      </c>
-      <c r="J137" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -9236,31 +9230,31 @@
         <v>142</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F138" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G138" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H138" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="I138" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="I138" s="1" t="s">
+      <c r="J138" t="s">
         <v>560</v>
-      </c>
-      <c r="J138" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -9268,31 +9262,31 @@
         <v>143</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="F139" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F139" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G139" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="H139" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="H139" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="I139" s="1" t="s">
+      <c r="J139" t="s">
         <v>564</v>
-      </c>
-      <c r="J139" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -9300,31 +9294,31 @@
         <v>144</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="G140" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="G140" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="H140" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="J140" t="s">
         <v>567</v>
-      </c>
-      <c r="J140" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -9332,31 +9326,31 @@
         <v>145</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G141" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H141" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="J141" t="s">
         <v>570</v>
-      </c>
-      <c r="J141" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -9364,31 +9358,31 @@
         <v>146</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F142" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G142" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="H142" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="H142" s="1" t="s">
+      <c r="I142" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="J142" t="s">
         <v>574</v>
-      </c>
-      <c r="J142" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -9396,31 +9390,31 @@
         <v>147</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F143" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G143" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H143" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="J143" t="s">
         <v>577</v>
-      </c>
-      <c r="J143" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -9428,31 +9422,31 @@
         <v>148</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G144" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="H144" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="I144" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="J144" t="s">
         <v>581</v>
-      </c>
-      <c r="J144" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -9460,31 +9454,31 @@
         <v>149</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F145" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G145" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H145" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="H145" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="I145" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="J145" t="s">
         <v>583</v>
-      </c>
-      <c r="J145" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -9492,31 +9486,31 @@
         <v>150</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="F146" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F146" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G146" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="H146" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="I146" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="J146" t="s">
         <v>587</v>
-      </c>
-      <c r="J146" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -9524,31 +9518,31 @@
         <v>151</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F147" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G147" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="H147" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="H147" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="I147" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="J147" t="s">
         <v>589</v>
-      </c>
-      <c r="J147" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -9556,31 +9550,31 @@
         <v>152</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F148" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G148" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="H148" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="H148" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="I148" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="J148" t="s">
         <v>591</v>
-      </c>
-      <c r="J148" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -9588,31 +9582,31 @@
         <v>153</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="E149" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="F149" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="F149" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="G149" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="H149" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="H149" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="I149" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J149" t="s">
         <v>593</v>
-      </c>
-      <c r="J149" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -9635,16 +9629,16 @@
         <v>148</v>
       </c>
       <c r="G150" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H150" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="I150" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="I150" s="1" t="s">
+      <c r="J150" t="s">
         <v>597</v>
-      </c>
-      <c r="J150" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -9667,16 +9661,16 @@
         <v>148</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="I151" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="J151" t="s">
         <v>601</v>
-      </c>
-      <c r="J151" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -9699,16 +9693,16 @@
         <v>148</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="I152" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="J152" t="s">
         <v>605</v>
-      </c>
-      <c r="J152" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -9731,16 +9725,16 @@
         <v>148</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="I153" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="J153" t="s">
         <v>609</v>
-      </c>
-      <c r="J153" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -9763,16 +9757,16 @@
         <v>148</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="I154" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="J154" t="s">
         <v>613</v>
-      </c>
-      <c r="J154" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9795,16 +9789,16 @@
         <v>148</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="I155" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="I155" s="1" t="s">
+      <c r="J155" t="s">
         <v>617</v>
-      </c>
-      <c r="J155" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9827,16 +9821,16 @@
         <v>148</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="I156" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="J156" t="s">
         <v>621</v>
-      </c>
-      <c r="J156" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9850,25 +9844,25 @@
         <v>435</v>
       </c>
       <c r="D157" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="F157" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="F157" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="H157" s="1" t="s">
+      <c r="I157" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="I157" s="1" t="s">
+      <c r="J157" t="s">
         <v>626</v>
-      </c>
-      <c r="J157" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9882,25 +9876,25 @@
         <v>435</v>
       </c>
       <c r="D158" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="F158" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="H158" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I158" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="I158" s="1" t="s">
+      <c r="J158" t="s">
         <v>629</v>
-      </c>
-      <c r="J158" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9914,25 +9908,25 @@
         <v>435</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="F159" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="H159" s="1" t="s">
+      <c r="I159" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="J159" t="s">
         <v>633</v>
-      </c>
-      <c r="J159" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9946,30 +9940,30 @@
         <v>435</v>
       </c>
       <c r="D160" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="F160" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" t="s">
         <v>636</v>
-      </c>
-      <c r="J160" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>10</v>
@@ -9984,24 +9978,24 @@
         <v>13</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="G161" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="H161" s="1" t="s">
+      <c r="I161" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="J161" t="s">
         <v>641</v>
-      </c>
-      <c r="J161" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>10</v>
@@ -10019,21 +10013,21 @@
         <v>95</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>96</v>
       </c>
       <c r="I162" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="J162" t="s">
         <v>644</v>
-      </c>
-      <c r="J162" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>10</v>
@@ -10051,21 +10045,21 @@
         <v>95</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H163" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I163" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="I163" s="1" t="s">
+      <c r="J163" t="s">
         <v>648</v>
-      </c>
-      <c r="J163" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>214</v>
@@ -10083,21 +10077,21 @@
         <v>218</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="I164" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="I164" s="1" t="s">
+      <c r="J164" t="s">
         <v>653</v>
-      </c>
-      <c r="J164" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>214</v>
@@ -10115,21 +10109,21 @@
         <v>218</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="I165" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="J165" t="s">
         <v>658</v>
-      </c>
-      <c r="J165" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>214</v>
@@ -10147,21 +10141,21 @@
         <v>218</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="H166" s="1" t="s">
+      <c r="I166" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="I166" s="1" t="s">
+      <c r="J166" t="s">
         <v>663</v>
-      </c>
-      <c r="J166" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>214</v>
@@ -10179,21 +10173,21 @@
         <v>218</v>
       </c>
       <c r="G167" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="I167" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="I167" s="1" t="s">
+      <c r="J167" t="s">
         <v>668</v>
-      </c>
-      <c r="J167" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>214</v>
@@ -10211,16 +10205,16 @@
         <v>328</v>
       </c>
       <c r="G168" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="H168" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="H168" s="1" t="s">
+      <c r="I168" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="I168" s="1" t="s">
+      <c r="J168" t="s">
         <v>673</v>
-      </c>
-      <c r="J168" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -10228,31 +10222,31 @@
         <v>170</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="D169" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="G169" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="G169" s="2" t="s">
+      <c r="H169" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="I169" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="I169" s="1" t="s">
+      <c r="J169" t="s">
         <v>694</v>
-      </c>
-      <c r="J169" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -10260,31 +10254,31 @@
         <v>171</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="D170" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E170" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="F170" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="G170" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="H170" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="I170" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="I170" s="1" t="s">
+      <c r="J170" t="s">
         <v>698</v>
-      </c>
-      <c r="J170" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -10292,31 +10286,31 @@
         <v>172</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="D171" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E171" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="F171" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="G171" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="H171" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="I171" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="I171" s="1" t="s">
+      <c r="J171" t="s">
         <v>702</v>
-      </c>
-      <c r="J171" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -10324,31 +10318,31 @@
         <v>173</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="D172" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E172" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="F172" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="G172" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="H172" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="H172" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="I172" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="J172" t="s">
         <v>704</v>
-      </c>
-      <c r="J172" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -10356,31 +10350,31 @@
         <v>174</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="D173" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="G173" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E173" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="G173" s="2" t="s">
+      <c r="H173" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="H173" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="I173" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="J173" t="s">
         <v>706</v>
-      </c>
-      <c r="J173" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -10388,31 +10382,31 @@
         <v>175</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>435</v>
+        <v>316</v>
       </c>
       <c r="D174" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="J174" t="s">
         <v>732</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="H174" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="I174" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="J174" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -10435,16 +10429,16 @@
         <v>218</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="J175" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -10467,16 +10461,16 @@
         <v>157</v>
       </c>
       <c r="G176" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="I176" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="J176" t="s">
         <v>745</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="J176" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -10484,31 +10478,31 @@
         <v>178</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>435</v>
+        <v>316</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>732</v>
+        <v>514</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G177" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="I177" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="H177" s="1" t="s">
+      <c r="J177" t="s">
         <v>752</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="J177" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -10531,16 +10525,16 @@
         <v>148</v>
       </c>
       <c r="G178" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="I178" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="H178" s="1" t="s">
+      <c r="J178" t="s">
         <v>756</v>
-      </c>
-      <c r="I178" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="J178" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -10563,16 +10557,16 @@
         <v>404</v>
       </c>
       <c r="G179" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="I179" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="H179" s="1" t="s">
+      <c r="J179" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="I179" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="J179" s="1" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -10595,16 +10589,16 @@
         <v>404</v>
       </c>
       <c r="G180" t="s">
+        <v>762</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="I180" t="s">
         <v>764</v>
       </c>
-      <c r="H180" s="1" t="s">
+      <c r="J180" t="s">
         <v>765</v>
-      </c>
-      <c r="I180" t="s">
-        <v>766</v>
-      </c>
-      <c r="J180" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -10627,16 +10621,16 @@
         <v>404</v>
       </c>
       <c r="G181" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="I181" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="H181" s="1" t="s">
+      <c r="J181" t="s">
         <v>769</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="J181" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -10650,25 +10644,25 @@
         <v>316</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="H182" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="I182" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="H182" s="1" t="s">
+      <c r="J182" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10682,25 +10676,25 @@
         <v>316</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="E183" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="F183" s="1" t="s">
+      <c r="G183" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="H183" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G183" s="1" t="s">
+      <c r="I183" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="J183" t="s">
         <v>781</v>
-      </c>
-      <c r="H183" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="J183" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -10714,25 +10708,25 @@
         <v>316</v>
       </c>
       <c r="D184" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="F184" s="1" t="s">
+      <c r="G184" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="H184" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G184" s="2" t="s">
+      <c r="I184" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="J184" t="s">
         <v>784</v>
-      </c>
-      <c r="H184" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="I184" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="J184" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -10746,25 +10740,25 @@
         <v>316</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F185" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="I185" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="G185" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="H185" s="1" t="s">
+      <c r="J185" t="s">
         <v>788</v>
-      </c>
-      <c r="I185" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="J185" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -10772,31 +10766,31 @@
         <v>187</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>434</v>
+        <v>892</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>435</v>
+        <v>803</v>
       </c>
       <c r="D186" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G186" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="E186" s="1" t="s">
+      <c r="H186" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="F186" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="G186" s="2" t="s">
+      <c r="I186" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="H186" s="1" t="s">
+      <c r="J186" t="s">
         <v>794</v>
-      </c>
-      <c r="I186" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="J186" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -10804,31 +10798,31 @@
         <v>188</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>434</v>
+        <v>892</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>435</v>
+        <v>803</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G187" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="I187" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="H187" s="1" t="s">
+      <c r="J187" t="s">
         <v>798</v>
-      </c>
-      <c r="I187" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="J187" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -10836,31 +10830,31 @@
         <v>189</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>434</v>
+        <v>892</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>435</v>
+        <v>803</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G188" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="I188" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="H188" s="1" t="s">
+      <c r="J188" t="s">
         <v>802</v>
-      </c>
-      <c r="I188" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="J188" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -10868,31 +10862,31 @@
         <v>190</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="F189" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="G189" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="H189" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="F189" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="G189" s="2" t="s">
+      <c r="I189" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="H189" s="1" t="s">
+      <c r="J189" t="s">
         <v>809</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="J189" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -10900,31 +10894,31 @@
         <v>191</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C190" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F190" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G190" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="I190" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="H190" s="1" t="s">
+      <c r="J190" t="s">
         <v>813</v>
-      </c>
-      <c r="I190" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="J190" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -10932,31 +10926,31 @@
         <v>192</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F191" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G191" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="I191" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="H191" s="1" t="s">
+      <c r="J191" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -10964,31 +10958,31 @@
         <v>193</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F192" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G192" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="I192" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="H192" s="1" t="s">
+      <c r="J192" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -10996,31 +10990,31 @@
         <v>194</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C193" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F193" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G193" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="I193" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="H193" s="1" t="s">
+      <c r="J193" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="I193" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="J193" s="1" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -11028,31 +11022,31 @@
         <v>195</v>
       </c>
       <c r="B194" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C194" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F194" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G194" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="I194" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="H194" s="1" t="s">
+      <c r="J194" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="I194" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -11060,31 +11054,31 @@
         <v>196</v>
       </c>
       <c r="B195" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C195" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D195" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F195" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G195" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="I195" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="H195" s="1" t="s">
+      <c r="J195" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="I195" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="J195" s="1" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -11092,31 +11086,31 @@
         <v>197</v>
       </c>
       <c r="B196" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C196" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F196" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G196" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="I196" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="H196" s="1" t="s">
+      <c r="J196" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="J196" s="1" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -11124,31 +11118,31 @@
         <v>198</v>
       </c>
       <c r="B197" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C197" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F197" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G197" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="I197" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="H197" s="1" t="s">
+      <c r="J197" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="I197" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="J197" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -11156,31 +11150,31 @@
         <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C198" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F198" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G198" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="I198" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="H198" s="1" t="s">
+      <c r="J198" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="I198" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="J198" s="1" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -11188,31 +11182,31 @@
         <v>200</v>
       </c>
       <c r="B199" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C199" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F199" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G199" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="I199" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="H199" s="1" t="s">
+      <c r="J199" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="I199" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="J199" s="1" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -11220,31 +11214,31 @@
         <v>201</v>
       </c>
       <c r="B200" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C200" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D200" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="F200" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G200" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="I200" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="H200" s="1" t="s">
+      <c r="J200" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="I200" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="J200" s="1" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -11252,31 +11246,31 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="G201" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="E201" s="1" t="s">
+      <c r="H201" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="F201" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="G201" s="1" t="s">
+      <c r="I201" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="H201" s="1" t="s">
+      <c r="J201" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="I201" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -11284,31 +11278,31 @@
         <v>203</v>
       </c>
       <c r="B202" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G202" t="s">
+        <v>860</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="I202" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="H202" s="1" t="s">
+      <c r="J202" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="I202" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="J202" s="1" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -11316,31 +11310,31 @@
         <v>204</v>
       </c>
       <c r="B203" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D203" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="F203" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="E203" s="1" t="s">
+      <c r="G203" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="H203" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="F203" s="1" t="s">
+      <c r="I203" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G203" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="H203" s="1" t="s">
+      <c r="J203" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="I203" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="J203" s="1" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -11348,31 +11342,31 @@
         <v>205</v>
       </c>
       <c r="B204" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D204" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="G204" t="s">
+        <v>870</v>
+      </c>
+      <c r="H204" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="E204" s="1" t="s">
+      <c r="I204" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="F204" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="G204" t="s">
-        <v>872</v>
-      </c>
-      <c r="H204" s="1" t="s">
+      <c r="J204" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="I204" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="J204" s="1" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -11380,31 +11374,31 @@
         <v>206</v>
       </c>
       <c r="B205" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="G205" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="H205" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="I205" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="F205" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="G205" s="1" t="s">
+      <c r="J205" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -11412,31 +11406,31 @@
         <v>207</v>
       </c>
       <c r="B206" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G206" t="s">
+        <v>880</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="J206" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="I206" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="J206" s="1" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -11444,31 +11438,31 @@
         <v>208</v>
       </c>
       <c r="B207" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D207" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="G207" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="E207" s="1" t="s">
+      <c r="H207" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="I207" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="F207" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="G207" s="1" t="s">
+      <c r="J207" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="I207" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="J207" s="1" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -11476,31 +11470,31 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="G208" t="s">
+        <v>888</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="I208" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="E208" s="1" t="s">
+      <c r="J208" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="G208" t="s">
-        <v>890</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="I208" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="J208" s="1" t="s">
-        <v>893</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D58FE-CE6B-4ECD-9102-72CA24C5B84B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFDB261-52FD-4D95-882B-78BEF0ACDFA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="913">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -3088,9 +3088,6 @@
     <t>child3_big_163.jpg</t>
   </si>
   <si>
-    <t>Напівмуфта ніпель БРС ЄВРО для гідравлічних систем</t>
-  </si>
-  <si>
     <t>Ніпель (вставна частина) швидкороз’ємного з’єднання стандарту ISO 7241-A є універсальним
 елементом для оперативного підключення гідравлічного обладнання. Має уніфікований форм-фактор,
 що забезпечує повну сумісність із розетками відповідного типорозміру незалежно від виробника, та
@@ -3152,19 +3149,6 @@
   </si>
   <si>
     <t>26b</t>
-  </si>
-  <si>
-    <t>Швидкорознімний прямий з’єднувач із цанговим приєднанням для пластикових трубок та зовнішньою
-приєднувальною різьбою призначений для підключення до різних пневматичних вузлів та агрегатів.
-Фіксація трубки здійснюється цанговим затискним механізмом, який надійно утримує її в зоні герметичного
-ущільнення. Вбудована розпірна (розблокувальна) втулка при натисканні розтискає цанговий елемент і
-забезпечує безпечне вилучення трубки.
-Конструкція забезпечує стабільну герметичність різьбового та трубного з’єднання, зберігає геометрію трубки
-без її деформації та допускає багаторазове використання з’єднувача.
-Особливості та властивості:
-1. Матеріал корпусу — алюміній
-2. Матеріал цангового механізму та розпірної втулки — алюміній
-3. Матеріал ущільнювального кільця — NBR (бутадієн-нітрильний каучук)</t>
   </si>
   <si>
     <t>child3_small_26b.jpg</t>
@@ -3545,12 +3529,6 @@
   </si>
   <si>
     <t>Наконечник для підкачування шин із затискним пластиковим важелем та кутовим виходом «ялинка»</t>
-  </si>
-  <si>
-    <t>З'єднувач пневматичний прямий цанговий подовжений</t>
-  </si>
-  <si>
-    <t>З'єднувач перехідний пневматичний прямий із цанговим приєднанням та зовнішньою різьбою подовжений</t>
   </si>
   <si>
     <t>З'єднувач пневматичний перехідний Т-подібний із самозамикаючою швидкороз'ємною муфтою та двома прямими цанговими виходами</t>
@@ -4473,6 +4451,100 @@
   </si>
   <si>
     <t>Муфта ШРЗ з одностороннім розніманням  (розривна) для гідравлічних систем</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пневматичні з’єднувальні елементи для гальмівних і допоміжних систем транспортних засобів Norgren Fleetfit 97400 </t>
+  </si>
+  <si>
+    <t>Швидкорознімний прямий цанговий з’єднувач призначений для оперативного монтажу та демонтажупластикових пневматичних трубок без застосування інструменту.
+Призначений для високонадійного підключення до різних автомобільних пневматичних вузлів, ресиверів та виконавчих агрегатів. Розроблений за технологією IMI Norgren — визнаним світовим стандартом для первинної комплектації (OEM) та ремонту пневматичних гальмівних систем комерційного транспорту.
+Особливості та властивості матеріалів:
+Матеріал корпусу — високоякісна суцільна латунь, що гарантує стійкість до ударів каміння, дорожніх реагентів та агресивного зовнішнього середовища.
+Матеріал цанги — суцільна латунь; спеціальна геометрія затискних зубців забезпечує надійну фіксацію трубки одним рухом без ризику її деформації.
+Матеріал упорної (розпірної) втулки — латунь; інтегрована в конструкцію порту для підтримки внутрішніх стінок трубки та захисту від зминання під робочим тиском.
+Матеріал ущільнювального кільця — спеціалізований морозостійкий бутадієн-нітрильний каучук (NBR), який зберігає еластичність за умов критично низьких температур і стійкий до компресорної оливи.
+Технічні параметри:
+Робоче середовище: підготовлене стиснене повітря пневматичних систем.
+Робочий тиск: від 0 до 10 бар (від 0 до 145 psi).Діапазон робочих температур: від -40°C до +100°C (від -40°F до +212°F).
+Сфера застосування: комерційний автотранспорт (вантажівки, автобуси, причепи та спецтехніка).
+Серія продукту: Fleetfit 97400.
+Сумісність із трубками: поліамідні трубки (PA 11/12) відповідно до стандарту DIN 74324.
+Сертифікація безпеки: схвалено німецьким інститутом TÜV, відповідає вимогам DOT FMVSS 106 та SAE J1131.</t>
+  </si>
+  <si>
+    <t>Швидкорознімний прямий з’єднувач із цанговим приєднанням типу Push-In для пластикових трубок та зовнішньою приєднувальною різьбою. Призначений для високонадійного підключення до різних автомобільних пневматичних вузлів, ресиверів та виконавчих агрегатів. Розроблений за технологією IMI Norgren — визнаним світовим стандартом для первинної комплектації (OEM) та ремонту пневматичних гальмівних систем комерційного транспорту.
+Особливості та властивості матеріалів:
+Матеріал корпусу — високоякісна суцільна латунь, що гарантує стійкість до ударів каміння, дорожніх реагентів та агресивного зовнішнього середовища.
+Матеріал цанги — суцільна латунь; спеціальна геометрія затискних зубців забезпечує надійну фіксацію трубки одним рухом без ризику її деформації.
+Матеріал упорної (розпірної) втулки — латунь; інтегрована в конструкцію порту для підтримки внутрішніх стінок трубки та захисту від зминання під робочим тиском.
+Матеріал ущільнювального кільця — спеціалізований морозостійкий бутадієн-нітрильний каучук (NBR), який зберігає еластичність за умов критично низьких температур і стійкий до компресорної оливи.
+Технічні параметри:
+Робоче середовище: підготовлене стиснене повітря пневматичних систем.
+Робочий тиск: від 0 до 10 бар (від 0 до 145 psi).Діапазон робочих температур: від -40°C до +100°C (від -40°F до +212°F).
+Сфера застосування: комерційний автотранспорт (вантажівки, автобуси, причепи та спецтехніка).
+Серія продукту: Fleetfit 97400.
+Сумісність із трубками: поліамідні трубки (PA 11/12) відповідно до стандарту DIN 74324.
+Сертифікація безпеки: схвалено німецьким інститутом TÜV, відповідає вимогам DOT FMVSS 106 та SAE J1131.</t>
+  </si>
+  <si>
+    <t>Гайка пневмоз`єднання стопорна</t>
+  </si>
+  <si>
+    <t>Гайка пневмоз’єднання стопорна (контргайка) із внутрішньою різьбою призначена для фіксації, регулювання та запобігання самовільному розкручуванню різьбових елементів (штуцерів, адаптерів, перехідників) у гальмівних та допоміжних пневматичних системах вантажного автомобільного транспорту, причепів, напівпричепів та спецтехніки. Вона забезпечує надійне позиціонування кутових або трійникових з’єднувачів у корпусах клапанів, блоків керування чи ресиверів.
+Стопоріння та ущільнення вузла здійснюється за рахунок спеціальної конструкції гайки, що працює в зоні приєднання штуцера. Вона надійно фіксує елемент у заданому положенні, компенсуючи вібраційні навантаження під час руху автомобіля. Гайка виконана у звуженому (вузькому) профілі під ключ SW28 та інтегрована зі спеціальним еластичним кільцем ущільнення, що гарантує герметичність з’єднання після затягування. Конструкція захищає різьбову зону від потрапляння вологи, дорожньої грязі та запобігає витоку стисненого повітря.
+Корпус гайки виготовлений із високоякісного металу (латуні), що забезпечує максимальну механічну міцність, стійкість до деформацій при затягуванні, а також абсолютну тривалу стійкість до корозії та агресивного впливу зовнішнього середовища. Завдяки цьому деталь придатна для роботи в умовах високих термічних і вібраційних навантажень, які є характерними для пневмосистем комерційної техніки.
+Конструкція виробу зберігає цілісність суміжних деталей під час монтажу, підтримує стабільну щільність з’єднання під високим робочим тиском та допускає багаторазове використання під час проведення ремонтних або сервісних робіт без погіршення експлуатаційних характеристик.
+Особливості та властивості:
+1. Матеріал корпусу гайки — латунь (висока міцність та захист від окислення).
+2. Матеріал інтегрованого ущільнювального кільця — NBR (бутадієн-нітрильний каучук), стійкий до мастил, температурних коливань та стисненого повітря.</t>
+  </si>
+  <si>
+    <t>child3_small_210.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_210.jpg</t>
+  </si>
+  <si>
+    <t>Клапан запобіжний для компресора</t>
+  </si>
+  <si>
+    <t>Запобіжний клапан призначений для запобігання перевищенню тиску в компресорі. При досягненні 8 атм він автоматично скидає надлишкове повітря, підтримуючи стабільну роботу системи. Надійний латунний корпус забезпечує довговічність і стійкість до корозії. Підходить для більшості компресорів і ресиверів.</t>
+  </si>
+  <si>
+    <t>child3_small_211.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_211.jpg</t>
+  </si>
+  <si>
+    <t>child1_31.jpg</t>
+  </si>
+  <si>
+    <t>Напівмуфти з’єднувальні для гідравлічних систем</t>
+  </si>
+  <si>
+    <t>Напівмуфта ніпель  БРС для гідравлічних систем</t>
+  </si>
+  <si>
+    <t>Напівмуфта гніздо БРС для гідравлічних систем</t>
+  </si>
+  <si>
+    <t>Гніздо швидкороз’ємного з’єднання стандарту ISO 7241-A є універсальним
+елементом для оперативного підключення гідравлічного обладнання. Має уніфікований форм-фактор,
+що забезпечує повну сумісність із розетками відповідного типорозміру незалежно від виробника, та
+оснащений вбудованим запірним клапаном, який запобігає витоку гідравлічної рідини під час
+роз’єднання.
+Особливості та властивості:
+1. Матеріал ніпеля- вуглецева сталь з зовнішнім і внутрішнім гальванічним цинковим покриттям, що
+забезпечує герметичне з'єднання, тривалий термін служби і високу корозійну стійкість.
+2. Номінальний робочий тиск - 250 bar.
+3. Ніпель укомплектований захисним гумовим ковпачком і транспортувальною кришкою</t>
+  </si>
+  <si>
+    <t>child3_small_212.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_212.jpg</t>
   </si>
 </sst>
 </file>
@@ -4509,14 +4581,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4832,7 +4901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5309,10 +5378,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>67</v>
@@ -5981,7 +6050,7 @@
         <v>148</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>149</v>
@@ -6013,7 +6082,7 @@
         <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>152</v>
@@ -6025,7 +6094,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -6035,7 +6104,7 @@
       <c r="C38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -6409,7 +6478,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6419,7 +6488,7 @@
       <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -6429,10 +6498,10 @@
         <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>210</v>
@@ -6441,7 +6510,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -6451,7 +6520,7 @@
       <c r="C51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>155</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -6461,10 +6530,10 @@
         <v>157</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>212</v>
@@ -6653,10 +6722,10 @@
         <v>218</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>239</v>
@@ -7191,7 +7260,7 @@
         <v>317</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>317</v>
@@ -7223,13 +7292,13 @@
         <v>317</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>318</v>
@@ -7255,13 +7324,13 @@
         <v>317</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>318</v>
@@ -7287,13 +7356,13 @@
         <v>317</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>323</v>
@@ -7319,13 +7388,13 @@
         <v>317</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>317</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>323</v>
@@ -7965,16 +8034,16 @@
         <v>328</v>
       </c>
       <c r="G98" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="J98" t="s">
         <v>675</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="J98" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -7997,16 +8066,16 @@
         <v>328</v>
       </c>
       <c r="G99" t="s">
+        <v>676</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="J99" t="s">
         <v>679</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="J99" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -8029,16 +8098,16 @@
         <v>328</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="H100" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="J100" t="s">
         <v>683</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="J100" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -8061,16 +8130,16 @@
         <v>328</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H101" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="J101" t="s">
         <v>686</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="J101" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -8841,7 +8910,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>129</v>
       </c>
@@ -8851,7 +8920,7 @@
       <c r="C126" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E126" s="1" t="s">
@@ -8873,7 +8942,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>130</v>
       </c>
@@ -8883,7 +8952,7 @@
       <c r="C127" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E127" s="1" t="s">
@@ -8905,7 +8974,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>131</v>
       </c>
@@ -8915,17 +8984,17 @@
       <c r="C128" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>515</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>516</v>
@@ -8937,7 +9006,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>132</v>
       </c>
@@ -8947,17 +9016,17 @@
       <c r="C129" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>515</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>519</v>
@@ -8969,7 +9038,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>133</v>
       </c>
@@ -8979,14 +9048,14 @@
       <c r="C130" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" s="1" t="s">
         <v>514</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>515</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>522</v>
@@ -9085,10 +9154,10 @@
         <v>539</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>541</v>
@@ -9117,10 +9186,10 @@
         <v>539</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>544</v>
@@ -9149,10 +9218,10 @@
         <v>539</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>547</v>
@@ -9469,10 +9538,10 @@
         <v>539</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>582</v>
@@ -9533,10 +9602,10 @@
         <v>539</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>588</v>
@@ -9565,10 +9634,10 @@
         <v>539</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>590</v>
@@ -9597,10 +9666,10 @@
         <v>539</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>592</v>
@@ -9853,7 +9922,7 @@
         <v>622</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>624</v>
@@ -9885,7 +9954,7 @@
         <v>622</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>627</v>
@@ -9914,19 +9983,19 @@
         <v>623</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>622</v>
+        <v>907</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="H159" s="1" t="s">
+      <c r="I159" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="J159" t="s">
         <v>632</v>
-      </c>
-      <c r="J159" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9949,21 +10018,21 @@
         <v>622</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="H160" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="J160" t="s">
         <v>635</v>
-      </c>
-      <c r="J160" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>10</v>
@@ -9978,24 +10047,24 @@
         <v>13</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="G161" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="H161" s="1" t="s">
+      <c r="I161" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="I161" s="1" t="s">
+      <c r="J161" t="s">
         <v>640</v>
-      </c>
-      <c r="J161" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>10</v>
@@ -10004,30 +10073,30 @@
         <v>11</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>12</v>
+        <v>895</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>13</v>
+        <v>906</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>95</v>
+        <v>895</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>727</v>
+        <v>15</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>96</v>
+        <v>896</v>
       </c>
       <c r="I162" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J162" t="s">
         <v>643</v>
-      </c>
-      <c r="J162" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>10</v>
@@ -10036,30 +10105,30 @@
         <v>11</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>12</v>
+        <v>895</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>13</v>
+        <v>906</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>95</v>
+        <v>895</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>728</v>
+        <v>39</v>
       </c>
       <c r="H163" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="J163" t="s">
         <v>646</v>
-      </c>
-      <c r="I163" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="J163" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>214</v>
@@ -10077,21 +10146,21 @@
         <v>218</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I164" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="J164" t="s">
         <v>651</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="J164" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>214</v>
@@ -10109,21 +10178,21 @@
         <v>218</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="J165" t="s">
         <v>656</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="J165" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>214</v>
@@ -10141,21 +10210,21 @@
         <v>218</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="I166" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="H166" s="1" t="s">
+      <c r="J166" t="s">
         <v>661</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="J166" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>214</v>
@@ -10173,21 +10242,21 @@
         <v>218</v>
       </c>
       <c r="G167" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I167" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="J167" t="s">
         <v>666</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="J167" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>214</v>
@@ -10205,16 +10274,16 @@
         <v>328</v>
       </c>
       <c r="G168" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="H168" s="1" t="s">
+      <c r="J168" t="s">
         <v>671</v>
-      </c>
-      <c r="I168" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="J168" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -10228,25 +10297,25 @@
         <v>536</v>
       </c>
       <c r="D169" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="E169" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="G169" s="2" t="s">
+      <c r="I169" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="J169" t="s">
         <v>692</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="J169" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -10260,25 +10329,25 @@
         <v>536</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G170" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I170" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="J170" t="s">
         <v>696</v>
-      </c>
-      <c r="I170" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="J170" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -10292,25 +10361,25 @@
         <v>536</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="I171" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="J171" t="s">
         <v>700</v>
-      </c>
-      <c r="I171" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="J171" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -10324,25 +10393,25 @@
         <v>536</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J172" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -10356,25 +10425,25 @@
         <v>536</v>
       </c>
       <c r="D173" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="E173" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="I173" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J173" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -10394,19 +10463,19 @@
         <v>515</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="J174" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -10429,16 +10498,16 @@
         <v>218</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="J175" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -10461,16 +10530,16 @@
         <v>157</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="J176" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -10490,19 +10559,19 @@
         <v>515</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="G177" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>750</v>
-      </c>
       <c r="I177" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="J177" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -10525,16 +10594,16 @@
         <v>148</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="J178" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -10557,16 +10626,16 @@
         <v>404</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -10589,16 +10658,16 @@
         <v>404</v>
       </c>
       <c r="G180" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="I180" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="J180" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -10621,16 +10690,16 @@
         <v>404</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="J181" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -10644,25 +10713,25 @@
         <v>316</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="H182" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="I182" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="J182" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10676,25 +10745,25 @@
         <v>316</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="H183" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="E183" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="H183" s="1" t="s">
+      <c r="I183" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="I183" s="1" t="s">
-        <v>780</v>
-      </c>
       <c r="J183" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -10708,25 +10777,25 @@
         <v>316</v>
       </c>
       <c r="D184" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="H184" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="H184" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="I184" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="J184" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -10740,25 +10809,25 @@
         <v>316</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="J185" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -10766,31 +10835,31 @@
         <v>187</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D186" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="I186" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E186" s="1" t="s">
+      <c r="J186" t="s">
         <v>790</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="H186" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="I186" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="J186" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -10798,31 +10867,31 @@
         <v>188</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="J187" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -10830,31 +10899,31 @@
         <v>189</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="J188" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -10862,31 +10931,31 @@
         <v>190</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="H189" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="I189" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="J189" t="s">
         <v>805</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="H189" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="I189" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="J189" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -10894,31 +10963,31 @@
         <v>191</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F190" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="J190" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -10926,31 +10995,31 @@
         <v>192</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -10958,31 +11027,31 @@
         <v>193</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -10990,31 +11059,31 @@
         <v>194</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -11022,31 +11091,31 @@
         <v>195</v>
       </c>
       <c r="B194" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -11054,31 +11123,31 @@
         <v>196</v>
       </c>
       <c r="B195" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -11086,31 +11155,31 @@
         <v>197</v>
       </c>
       <c r="B196" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -11118,31 +11187,31 @@
         <v>198</v>
       </c>
       <c r="B197" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -11150,31 +11219,31 @@
         <v>199</v>
       </c>
       <c r="B198" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -11182,31 +11251,31 @@
         <v>200</v>
       </c>
       <c r="B199" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -11214,31 +11283,31 @@
         <v>201</v>
       </c>
       <c r="B200" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -11246,31 +11315,31 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="I201" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="E201" s="1" t="s">
+      <c r="J201" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="I201" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -11278,31 +11347,31 @@
         <v>203</v>
       </c>
       <c r="B202" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G202" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -11310,31 +11379,31 @@
         <v>204</v>
       </c>
       <c r="B203" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D203" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="I203" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="E203" s="1" t="s">
+      <c r="J203" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="I203" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="J203" s="1" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -11342,31 +11411,31 @@
         <v>205</v>
       </c>
       <c r="B204" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D204" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="G204" t="s">
+        <v>866</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="I204" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="J204" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="G204" t="s">
-        <v>870</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="I204" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="J204" s="1" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -11374,31 +11443,31 @@
         <v>206</v>
       </c>
       <c r="B205" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="J205" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="J205" s="1" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -11406,31 +11475,31 @@
         <v>207</v>
       </c>
       <c r="B206" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="E206" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="G206" t="s">
         <v>876</v>
       </c>
-      <c r="F206" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="G206" t="s">
-        <v>880</v>
-      </c>
       <c r="H206" s="1" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -11438,31 +11507,31 @@
         <v>208</v>
       </c>
       <c r="B207" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D207" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="J207" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="I207" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="J207" s="1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -11470,31 +11539,127 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G208" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>891</v>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>210</v>
+      </c>
+      <c r="B209" t="s">
+        <v>214</v>
+      </c>
+      <c r="C209" t="s">
+        <v>215</v>
+      </c>
+      <c r="D209" t="s">
+        <v>328</v>
+      </c>
+      <c r="E209" t="s">
+        <v>329</v>
+      </c>
+      <c r="F209" t="s">
+        <v>328</v>
+      </c>
+      <c r="G209" t="s">
+        <v>898</v>
+      </c>
+      <c r="H209" t="s">
+        <v>899</v>
+      </c>
+      <c r="I209" t="s">
+        <v>900</v>
+      </c>
+      <c r="J209" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>211</v>
+      </c>
+      <c r="B210" t="s">
+        <v>315</v>
+      </c>
+      <c r="C210" t="s">
+        <v>316</v>
+      </c>
+      <c r="D210" t="s">
+        <v>514</v>
+      </c>
+      <c r="E210" t="s">
+        <v>515</v>
+      </c>
+      <c r="F210" t="s">
+        <v>902</v>
+      </c>
+      <c r="G210" t="s">
+        <v>902</v>
+      </c>
+      <c r="H210" t="s">
+        <v>903</v>
+      </c>
+      <c r="I210" t="s">
+        <v>904</v>
+      </c>
+      <c r="J210" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>212</v>
+      </c>
+      <c r="B211" t="s">
+        <v>434</v>
+      </c>
+      <c r="C211" t="s">
+        <v>435</v>
+      </c>
+      <c r="D211" t="s">
+        <v>622</v>
+      </c>
+      <c r="E211" t="s">
+        <v>623</v>
+      </c>
+      <c r="F211" t="s">
+        <v>907</v>
+      </c>
+      <c r="G211" t="s">
+        <v>909</v>
+      </c>
+      <c r="H211" t="s">
+        <v>910</v>
+      </c>
+      <c r="I211" t="s">
+        <v>911</v>
+      </c>
+      <c r="J211" t="s">
+        <v>912</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFDB261-52FD-4D95-882B-78BEF0ACDFA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F761318-E521-49CC-87CA-F2F96E070365}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Аркуш1!$A$1:$J$182</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="947">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -4456,22 +4456,6 @@
     <t xml:space="preserve">Пневматичні з’єднувальні елементи для гальмівних і допоміжних систем транспортних засобів Norgren Fleetfit 97400 </t>
   </si>
   <si>
-    <t>Швидкорознімний прямий цанговий з’єднувач призначений для оперативного монтажу та демонтажупластикових пневматичних трубок без застосування інструменту.
-Призначений для високонадійного підключення до різних автомобільних пневматичних вузлів, ресиверів та виконавчих агрегатів. Розроблений за технологією IMI Norgren — визнаним світовим стандартом для первинної комплектації (OEM) та ремонту пневматичних гальмівних систем комерційного транспорту.
-Особливості та властивості матеріалів:
-Матеріал корпусу — високоякісна суцільна латунь, що гарантує стійкість до ударів каміння, дорожніх реагентів та агресивного зовнішнього середовища.
-Матеріал цанги — суцільна латунь; спеціальна геометрія затискних зубців забезпечує надійну фіксацію трубки одним рухом без ризику її деформації.
-Матеріал упорної (розпірної) втулки — латунь; інтегрована в конструкцію порту для підтримки внутрішніх стінок трубки та захисту від зминання під робочим тиском.
-Матеріал ущільнювального кільця — спеціалізований морозостійкий бутадієн-нітрильний каучук (NBR), який зберігає еластичність за умов критично низьких температур і стійкий до компресорної оливи.
-Технічні параметри:
-Робоче середовище: підготовлене стиснене повітря пневматичних систем.
-Робочий тиск: від 0 до 10 бар (від 0 до 145 psi).Діапазон робочих температур: від -40°C до +100°C (від -40°F до +212°F).
-Сфера застосування: комерційний автотранспорт (вантажівки, автобуси, причепи та спецтехніка).
-Серія продукту: Fleetfit 97400.
-Сумісність із трубками: поліамідні трубки (PA 11/12) відповідно до стандарту DIN 74324.
-Сертифікація безпеки: схвалено німецьким інститутом TÜV, відповідає вимогам DOT FMVSS 106 та SAE J1131.</t>
-  </si>
-  <si>
     <t>Швидкорознімний прямий з’єднувач із цанговим приєднанням типу Push-In для пластикових трубок та зовнішньою приєднувальною різьбою. Призначений для високонадійного підключення до різних автомобільних пневматичних вузлів, ресиверів та виконавчих агрегатів. Розроблений за технологією IMI Norgren — визнаним світовим стандартом для первинної комплектації (OEM) та ремонту пневматичних гальмівних систем комерційного транспорту.
 Особливості та властивості матеріалів:
 Матеріал корпусу — високоякісна суцільна латунь, що гарантує стійкість до ударів каміння, дорожніх реагентів та агресивного зовнішнього середовища.
@@ -4545,6 +4529,111 @@
   </si>
   <si>
     <t>child3_big_212.jpg</t>
+  </si>
+  <si>
+    <t>З'єднувач пневматичний прямий цанговий подовжений</t>
+  </si>
+  <si>
+    <t>Швидкорознімний прямий цанговий з’єднувач призначений для оперативного монтажу та демонтажу пластикових пневматичних трубок без застосування інструменту. Фіксація трубки здійснюється цанговим затискним механізмом, який надійно утримує її в зоні герметичного ущільнення. Вбудована розпірна (розблокувальна) втулка при натисканні розтискає цанговий елемент і забезпечує безпечне вилучення трубки. Конструкція гарантує збереження геометрії трубки без її деформації, підтримує стабільну герметичність з’єднання та допускає багаторазове використання з’єднувача без погіршення експлуатаційних характеристик. Особливості та властивості: 1. Матеріал корпусу — алюміній 2. Матеріал цангового механізму та розпірної втулки — алюміній 3. Матеріал ущільнювального кільця — NBR (бутадієн-нітрильний каучук)</t>
+  </si>
+  <si>
+    <t>З'єднувач перехідний пневматичний прямий із цанговим приєднанням та зовнішньою різьбою подовжений</t>
+  </si>
+  <si>
+    <t>Швидкорознімний прямий з’єднувач із цанговим приєднанням для пластикових трубок та зовнішньою приєднувальною різьбою призначений для підключення до різних пневматичних вузлів та агрегатів. Фіксація трубки здійснюється цанговим затискним механізмом, який надійно утримує її в зоні герметичного ущільнення. Вбудована розпірна (розблокувальна) втулка при натисканні розтискає цанговий елемент і забезпечує безпечне вилучення трубки. Конструкція забезпечує стабільну герметичність різьбового та трубного з’єднання, зберігає геометрію трубки без її деформації та допускає багаторазове використання з’єднувача. Особливості та властивості: 1. Матеріал корпусу — алюміній 2. Матеріал цангового механізму та розпірної втулки — алюміній 3. Матеріал ущільнювального кільця — NBR (бутадієн-нітрильний каучук)</t>
+  </si>
+  <si>
+    <t>child3_small_213.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_213.jpg</t>
+  </si>
+  <si>
+    <t>Інструмент та витратні матеріали для обслуговування пневматичних систем</t>
+  </si>
+  <si>
+    <t>child1_32.jpg</t>
+  </si>
+  <si>
+    <t>Кільця гумові ущільнювальні для різьбових з’єднувальних елементів пневматичних систем</t>
+  </si>
+  <si>
+    <t>Кільця гумові ущільнювальні виготовлені відповідно до міжнародного стандарту ISO 3601 та призначені для герметизації різьбових з’єднань у пневматичних системах. Вони ефективно запобігають витоку стисненого повітря, забезпечуючи надійність і довговічність з’єднань. Завдяки спеціальному складу гумової суміші вироби зберігають високу еластичність та експлуатаційні властивості у широкому діапазоні температур: від -50°С до +100°С. Геометричні параметри та допуски кілець суворо відповідають вимогам ISO 3601, що гарантує їх ідеальну сумісність зі стандартними діаметрами пневматичних різьбових з’єднань. Особливості та властивості: матеріал (еластомер) – NBR (нітрил-бутадієновий каучук)</t>
+  </si>
+  <si>
+    <t>child3_small_214.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_214.jpg</t>
+  </si>
+  <si>
+    <t>Знімач для роз’єднання пневматичних трубок і з’єднувачів серії NEWLINE</t>
+  </si>
+  <si>
+    <t>Стандартний знімач для роз’єднання пластикових трубок із пневматичними з’єднувачами серії NEWLINE. Лінійка охоплює всі поширені типорозміри цієї серії; також доступний набір.</t>
+  </si>
+  <si>
+    <t>child3_small_215.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_215.jpg</t>
+  </si>
+  <si>
+    <t>Набір знімачів для роз'єднання пневматичних трубок та з'єднувачів серії NEWLINE*</t>
+  </si>
+  <si>
+    <t>Професійний набір знімачів для роз’єднання пластикових трубок із пневматичними з’єднувачами серії NEWLINE. Лінійка охоплює всі поширені типорозміри цієї серії.</t>
+  </si>
+  <si>
+    <t>child3_small_216.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_216.jpg</t>
+  </si>
+  <si>
+    <t>Набір знімачів для роз'єднання пневматичних трубок та з'єднувачів серії NEWLINE**</t>
+  </si>
+  <si>
+    <t>child3_small_217.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_217.jpg</t>
+  </si>
+  <si>
+    <t>Ножиці для пластикових трубок (D до 18 мм)</t>
+  </si>
+  <si>
+    <t>Професійний інструмент, спеціально розроблений для точного та рівного відрізання поліамідних (PA11, PA12), поліуретанових та інших пластикових трубок, що використовуються у пневматичних та паливних магістралях. Завдяки гострому лезу та ергономічній конструкції, ножиці забезпечують чистий зріз під прямим кутом без деформації стінок трубки. Це є критично важливою умовою для подальшого герметичного з’єднання з швидкороз’ємними фітингами (ШРЗ) та пневматичними з’єднувачами.</t>
+  </si>
+  <si>
+    <t>child3_small_218.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_218.jpg</t>
+  </si>
+  <si>
+    <t>Ножиці для пластикових трубок (D до 12 мм)</t>
+  </si>
+  <si>
+    <t>child3_small_219.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_219.jpg</t>
+  </si>
+  <si>
+    <t>Набір знімачів для роз'єднання пневматичних трубок та з'єднувачів серії NEWLINE</t>
+  </si>
+  <si>
+    <t>Ножиці для пластикових трубок</t>
+  </si>
+  <si>
+    <t>Набір знімачів для роз'єднання пневматичних трубок та з'єднувачів серії NEWLINE***</t>
+  </si>
+  <si>
+    <t>child3_small_220.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_220.jpg</t>
   </si>
 </sst>
 </file>
@@ -4901,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5002,7 +5091,7 @@
       <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5034,7 +5123,7 @@
       <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5066,7 +5155,7 @@
       <c r="I5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5098,7 +5187,7 @@
       <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5130,7 +5219,7 @@
       <c r="I7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5162,7 +5251,7 @@
       <c r="I8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5194,7 +5283,7 @@
       <c r="I9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5226,7 +5315,7 @@
       <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5258,7 +5347,7 @@
       <c r="I11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5290,7 +5379,7 @@
       <c r="I12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5322,7 +5411,7 @@
       <c r="I13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5354,7 +5443,7 @@
       <c r="I14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5386,7 +5475,7 @@
       <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5418,7 +5507,7 @@
       <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5450,7 +5539,7 @@
       <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>76</v>
       </c>
     </row>
@@ -5482,7 +5571,7 @@
       <c r="I18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5514,7 +5603,7 @@
       <c r="I19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5546,7 +5635,7 @@
       <c r="I20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5578,7 +5667,7 @@
       <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5610,7 +5699,7 @@
       <c r="I22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5642,7 +5731,7 @@
       <c r="I23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -5674,7 +5763,7 @@
       <c r="I24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5706,7 +5795,7 @@
       <c r="I25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5738,7 +5827,7 @@
       <c r="I26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5770,7 +5859,7 @@
       <c r="I27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5802,7 +5891,7 @@
       <c r="I28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5834,7 +5923,7 @@
       <c r="I29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5866,7 +5955,7 @@
       <c r="I30" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5898,7 +5987,7 @@
       <c r="I31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5930,7 +6019,7 @@
       <c r="I32" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5962,7 +6051,7 @@
       <c r="I33" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1" t="s">
         <v>134</v>
       </c>
     </row>
@@ -5994,7 +6083,7 @@
       <c r="I34" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6026,7 +6115,7 @@
       <c r="I35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6058,7 +6147,7 @@
       <c r="I36" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6090,7 +6179,7 @@
       <c r="I37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1" t="s">
         <v>154</v>
       </c>
     </row>
@@ -6122,7 +6211,7 @@
       <c r="I38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6154,7 +6243,7 @@
       <c r="I39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6186,7 +6275,7 @@
       <c r="I40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6218,7 +6307,7 @@
       <c r="I41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>176</v>
       </c>
     </row>
@@ -6250,7 +6339,7 @@
       <c r="I42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>180</v>
       </c>
     </row>
@@ -6282,7 +6371,7 @@
       <c r="I43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6314,7 +6403,7 @@
       <c r="I44" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6346,7 +6435,7 @@
       <c r="I45" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>192</v>
       </c>
     </row>
@@ -6378,7 +6467,7 @@
       <c r="I46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>196</v>
       </c>
     </row>
@@ -6410,7 +6499,7 @@
       <c r="I47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6442,7 +6531,7 @@
       <c r="I48" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6474,7 +6563,7 @@
       <c r="I49" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6506,7 +6595,7 @@
       <c r="I50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>211</v>
       </c>
     </row>
@@ -6538,7 +6627,7 @@
       <c r="I51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6570,7 +6659,7 @@
       <c r="I52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6602,7 +6691,7 @@
       <c r="I53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6634,7 +6723,7 @@
       <c r="I54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6666,7 +6755,7 @@
       <c r="I55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1" t="s">
         <v>234</v>
       </c>
     </row>
@@ -6698,7 +6787,7 @@
       <c r="I56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="1" t="s">
         <v>238</v>
       </c>
     </row>
@@ -6730,7 +6819,7 @@
       <c r="I57" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="1" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6762,7 +6851,7 @@
       <c r="I58" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="1" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6794,7 +6883,7 @@
       <c r="I59" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="1" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6826,7 +6915,7 @@
       <c r="I60" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="1" t="s">
         <v>255</v>
       </c>
     </row>
@@ -6858,7 +6947,7 @@
       <c r="I61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="1" t="s">
         <v>259</v>
       </c>
     </row>
@@ -6890,7 +6979,7 @@
       <c r="I62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="1" t="s">
         <v>263</v>
       </c>
     </row>
@@ -6922,7 +7011,7 @@
       <c r="I63" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="1" t="s">
         <v>270</v>
       </c>
     </row>
@@ -6954,7 +7043,7 @@
       <c r="I64" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="1" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6986,7 +7075,7 @@
       <c r="I65" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="1" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7018,7 +7107,7 @@
       <c r="I66" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="1" t="s">
         <v>282</v>
       </c>
     </row>
@@ -7050,7 +7139,7 @@
       <c r="I67" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="1" t="s">
         <v>286</v>
       </c>
     </row>
@@ -7082,7 +7171,7 @@
       <c r="I68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="1" t="s">
         <v>290</v>
       </c>
     </row>
@@ -7114,7 +7203,7 @@
       <c r="I69" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1" t="s">
         <v>294</v>
       </c>
     </row>
@@ -7146,7 +7235,7 @@
       <c r="I70" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="1" t="s">
         <v>298</v>
       </c>
     </row>
@@ -7178,7 +7267,7 @@
       <c r="I71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="1" t="s">
         <v>302</v>
       </c>
     </row>
@@ -7210,7 +7299,7 @@
       <c r="I72" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="1" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7242,7 +7331,7 @@
       <c r="I73" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="1" t="s">
         <v>310</v>
       </c>
     </row>
@@ -7274,7 +7363,7 @@
       <c r="I74" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="1" t="s">
         <v>314</v>
       </c>
     </row>
@@ -7306,7 +7395,7 @@
       <c r="I75" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="1" t="s">
         <v>320</v>
       </c>
     </row>
@@ -7338,7 +7427,7 @@
       <c r="I76" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="1" t="s">
         <v>322</v>
       </c>
     </row>
@@ -7370,7 +7459,7 @@
       <c r="I77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J77" s="1" t="s">
         <v>325</v>
       </c>
     </row>
@@ -7402,7 +7491,7 @@
       <c r="I78" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -7434,7 +7523,7 @@
       <c r="I79" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="1" t="s">
         <v>333</v>
       </c>
     </row>
@@ -7466,7 +7555,7 @@
       <c r="I80" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="1" t="s">
         <v>336</v>
       </c>
     </row>
@@ -7498,7 +7587,7 @@
       <c r="I81" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="1" t="s">
         <v>340</v>
       </c>
     </row>
@@ -7530,7 +7619,7 @@
       <c r="I82" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" s="1" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7562,7 +7651,7 @@
       <c r="I83" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="1" t="s">
         <v>348</v>
       </c>
     </row>
@@ -7594,7 +7683,7 @@
       <c r="I84" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="1" t="s">
         <v>352</v>
       </c>
     </row>
@@ -7626,7 +7715,7 @@
       <c r="I85" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="1" t="s">
         <v>356</v>
       </c>
     </row>
@@ -7658,7 +7747,7 @@
       <c r="I86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="1" t="s">
         <v>359</v>
       </c>
     </row>
@@ -7690,7 +7779,7 @@
       <c r="I87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="1" t="s">
         <v>363</v>
       </c>
     </row>
@@ -7722,7 +7811,7 @@
       <c r="I88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="1" t="s">
         <v>367</v>
       </c>
     </row>
@@ -7754,7 +7843,7 @@
       <c r="I89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="1" t="s">
         <v>371</v>
       </c>
     </row>
@@ -7786,7 +7875,7 @@
       <c r="I90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="1" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7818,7 +7907,7 @@
       <c r="I91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J91" s="1" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7850,7 +7939,7 @@
       <c r="I92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J92" s="1" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7882,7 +7971,7 @@
       <c r="I93" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" s="1" t="s">
         <v>387</v>
       </c>
     </row>
@@ -7914,7 +8003,7 @@
       <c r="I94" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J94" s="1" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7946,7 +8035,7 @@
       <c r="I95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J95" s="1" t="s">
         <v>395</v>
       </c>
     </row>
@@ -7978,7 +8067,7 @@
       <c r="I96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J96" s="1" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8010,7 +8099,7 @@
       <c r="I97" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J97" s="1" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8042,7 +8131,7 @@
       <c r="I98" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="J98" t="s">
+      <c r="J98" s="1" t="s">
         <v>675</v>
       </c>
     </row>
@@ -8065,7 +8154,7 @@
       <c r="F99" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G99" s="1" t="s">
         <v>676</v>
       </c>
       <c r="H99" s="1" t="s">
@@ -8074,7 +8163,7 @@
       <c r="I99" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="J99" t="s">
+      <c r="J99" s="1" t="s">
         <v>679</v>
       </c>
     </row>
@@ -8106,7 +8195,7 @@
       <c r="I100" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J100" s="1" t="s">
         <v>683</v>
       </c>
     </row>
@@ -8138,7 +8227,7 @@
       <c r="I101" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="1" t="s">
         <v>686</v>
       </c>
     </row>
@@ -8170,7 +8259,7 @@
       <c r="I102" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="J102" t="s">
+      <c r="J102" s="1" t="s">
         <v>409</v>
       </c>
     </row>
@@ -8202,7 +8291,7 @@
       <c r="I103" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" s="1" t="s">
         <v>413</v>
       </c>
     </row>
@@ -8234,7 +8323,7 @@
       <c r="I104" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J104" s="1" t="s">
         <v>417</v>
       </c>
     </row>
@@ -8266,7 +8355,7 @@
       <c r="I105" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J105" t="s">
+      <c r="J105" s="1" t="s">
         <v>421</v>
       </c>
     </row>
@@ -8298,7 +8387,7 @@
       <c r="I106" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J106" s="1" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8330,7 +8419,7 @@
       <c r="I107" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J107" s="1" t="s">
         <v>429</v>
       </c>
     </row>
@@ -8362,7 +8451,7 @@
       <c r="I108" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J108" s="1" t="s">
         <v>433</v>
       </c>
     </row>
@@ -8394,7 +8483,7 @@
       <c r="I109" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J109" s="1" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8426,7 +8515,7 @@
       <c r="I110" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J110" t="s">
+      <c r="J110" s="1" t="s">
         <v>445</v>
       </c>
     </row>
@@ -8458,7 +8547,7 @@
       <c r="I111" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="J111" t="s">
+      <c r="J111" s="1" t="s">
         <v>449</v>
       </c>
     </row>
@@ -8490,7 +8579,7 @@
       <c r="I112" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="J112" t="s">
+      <c r="J112" s="1" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8522,7 +8611,7 @@
       <c r="I113" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="J113" t="s">
+      <c r="J113" s="1" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8554,7 +8643,7 @@
       <c r="I114" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="J114" t="s">
+      <c r="J114" s="1" t="s">
         <v>461</v>
       </c>
     </row>
@@ -8586,7 +8675,7 @@
       <c r="I115" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="J115" t="s">
+      <c r="J115" s="1" t="s">
         <v>465</v>
       </c>
     </row>
@@ -8618,7 +8707,7 @@
       <c r="I116" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="J116" t="s">
+      <c r="J116" s="1" t="s">
         <v>469</v>
       </c>
     </row>
@@ -8650,7 +8739,7 @@
       <c r="I117" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J117" t="s">
+      <c r="J117" s="1" t="s">
         <v>473</v>
       </c>
     </row>
@@ -8682,7 +8771,7 @@
       <c r="I118" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="J118" t="s">
+      <c r="J118" s="1" t="s">
         <v>477</v>
       </c>
     </row>
@@ -8714,7 +8803,7 @@
       <c r="I119" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="J119" t="s">
+      <c r="J119" s="1" t="s">
         <v>481</v>
       </c>
     </row>
@@ -8746,7 +8835,7 @@
       <c r="I120" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J120" t="s">
+      <c r="J120" s="1" t="s">
         <v>483</v>
       </c>
     </row>
@@ -8778,7 +8867,7 @@
       <c r="I121" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="J121" t="s">
+      <c r="J121" s="1" t="s">
         <v>487</v>
       </c>
     </row>
@@ -8810,7 +8899,7 @@
       <c r="I122" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J122" t="s">
+      <c r="J122" s="1" t="s">
         <v>491</v>
       </c>
     </row>
@@ -8842,7 +8931,7 @@
       <c r="I123" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J123" t="s">
+      <c r="J123" s="1" t="s">
         <v>495</v>
       </c>
     </row>
@@ -8874,7 +8963,7 @@
       <c r="I124" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="J124" t="s">
+      <c r="J124" s="1" t="s">
         <v>499</v>
       </c>
     </row>
@@ -8906,7 +8995,7 @@
       <c r="I125" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="J125" t="s">
+      <c r="J125" s="1" t="s">
         <v>503</v>
       </c>
     </row>
@@ -8938,7 +9027,7 @@
       <c r="I126" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="J126" t="s">
+      <c r="J126" s="1" t="s">
         <v>508</v>
       </c>
     </row>
@@ -8970,7 +9059,7 @@
       <c r="I127" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="J127" t="s">
+      <c r="J127" s="1" t="s">
         <v>513</v>
       </c>
     </row>
@@ -9002,7 +9091,7 @@
       <c r="I128" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J128" t="s">
+      <c r="J128" s="1" t="s">
         <v>518</v>
       </c>
     </row>
@@ -9034,7 +9123,7 @@
       <c r="I129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="J129" t="s">
+      <c r="J129" s="1" t="s">
         <v>521</v>
       </c>
     </row>
@@ -9066,7 +9155,7 @@
       <c r="I130" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="J130" t="s">
+      <c r="J130" s="1" t="s">
         <v>525</v>
       </c>
     </row>
@@ -9098,7 +9187,7 @@
       <c r="I131" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="J131" t="s">
+      <c r="J131" s="1" t="s">
         <v>530</v>
       </c>
     </row>
@@ -9130,7 +9219,7 @@
       <c r="I132" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="J132" t="s">
+      <c r="J132" s="1" t="s">
         <v>534</v>
       </c>
     </row>
@@ -9162,7 +9251,7 @@
       <c r="I133" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="J133" t="s">
+      <c r="J133" s="1" t="s">
         <v>542</v>
       </c>
     </row>
@@ -9194,7 +9283,7 @@
       <c r="I134" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="J134" t="s">
+      <c r="J134" s="1" t="s">
         <v>545</v>
       </c>
     </row>
@@ -9226,7 +9315,7 @@
       <c r="I135" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="J135" t="s">
+      <c r="J135" s="1" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9258,7 +9347,7 @@
       <c r="I136" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="J136" t="s">
+      <c r="J136" s="1" t="s">
         <v>552</v>
       </c>
     </row>
@@ -9290,7 +9379,7 @@
       <c r="I137" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J137" t="s">
+      <c r="J137" s="1" t="s">
         <v>556</v>
       </c>
     </row>
@@ -9322,7 +9411,7 @@
       <c r="I138" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="J138" t="s">
+      <c r="J138" s="1" t="s">
         <v>560</v>
       </c>
     </row>
@@ -9354,7 +9443,7 @@
       <c r="I139" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="J139" t="s">
+      <c r="J139" s="1" t="s">
         <v>564</v>
       </c>
     </row>
@@ -9386,7 +9475,7 @@
       <c r="I140" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="J140" t="s">
+      <c r="J140" s="1" t="s">
         <v>567</v>
       </c>
     </row>
@@ -9418,7 +9507,7 @@
       <c r="I141" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="J141" t="s">
+      <c r="J141" s="1" t="s">
         <v>570</v>
       </c>
     </row>
@@ -9450,7 +9539,7 @@
       <c r="I142" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="J142" t="s">
+      <c r="J142" s="1" t="s">
         <v>574</v>
       </c>
     </row>
@@ -9482,7 +9571,7 @@
       <c r="I143" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="J143" t="s">
+      <c r="J143" s="1" t="s">
         <v>577</v>
       </c>
     </row>
@@ -9514,7 +9603,7 @@
       <c r="I144" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="J144" t="s">
+      <c r="J144" s="1" t="s">
         <v>581</v>
       </c>
     </row>
@@ -9546,7 +9635,7 @@
       <c r="I145" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="J145" t="s">
+      <c r="J145" s="1" t="s">
         <v>583</v>
       </c>
     </row>
@@ -9578,7 +9667,7 @@
       <c r="I146" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="J146" t="s">
+      <c r="J146" s="1" t="s">
         <v>587</v>
       </c>
     </row>
@@ -9610,7 +9699,7 @@
       <c r="I147" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="J147" t="s">
+      <c r="J147" s="1" t="s">
         <v>589</v>
       </c>
     </row>
@@ -9642,7 +9731,7 @@
       <c r="I148" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="J148" t="s">
+      <c r="J148" s="1" t="s">
         <v>591</v>
       </c>
     </row>
@@ -9674,7 +9763,7 @@
       <c r="I149" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="J149" t="s">
+      <c r="J149" s="1" t="s">
         <v>593</v>
       </c>
     </row>
@@ -9706,7 +9795,7 @@
       <c r="I150" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="J150" t="s">
+      <c r="J150" s="1" t="s">
         <v>597</v>
       </c>
     </row>
@@ -9738,7 +9827,7 @@
       <c r="I151" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J151" t="s">
+      <c r="J151" s="1" t="s">
         <v>601</v>
       </c>
     </row>
@@ -9770,7 +9859,7 @@
       <c r="I152" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="J152" t="s">
+      <c r="J152" s="1" t="s">
         <v>605</v>
       </c>
     </row>
@@ -9802,7 +9891,7 @@
       <c r="I153" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="J153" t="s">
+      <c r="J153" s="1" t="s">
         <v>609</v>
       </c>
     </row>
@@ -9834,7 +9923,7 @@
       <c r="I154" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="J154" t="s">
+      <c r="J154" s="1" t="s">
         <v>613</v>
       </c>
     </row>
@@ -9866,7 +9955,7 @@
       <c r="I155" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="J155" t="s">
+      <c r="J155" s="1" t="s">
         <v>617</v>
       </c>
     </row>
@@ -9898,7 +9987,7 @@
       <c r="I156" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="J156" t="s">
+      <c r="J156" s="1" t="s">
         <v>621</v>
       </c>
     </row>
@@ -9930,7 +10019,7 @@
       <c r="I157" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="J157" t="s">
+      <c r="J157" s="1" t="s">
         <v>626</v>
       </c>
     </row>
@@ -9962,7 +10051,7 @@
       <c r="I158" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J158" t="s">
+      <c r="J158" s="1" t="s">
         <v>629</v>
       </c>
     </row>
@@ -9983,10 +10072,10 @@
         <v>623</v>
       </c>
       <c r="F159" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>630</v>
@@ -9994,7 +10083,7 @@
       <c r="I159" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J159" t="s">
+      <c r="J159" s="1" t="s">
         <v>632</v>
       </c>
     </row>
@@ -10026,7 +10115,7 @@
       <c r="I160" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="J160" t="s">
+      <c r="J160" s="1" t="s">
         <v>635</v>
       </c>
     </row>
@@ -10037,7 +10126,7 @@
       <c r="B161" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -10058,7 +10147,7 @@
       <c r="I161" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="J161" t="s">
+      <c r="J161" s="1" t="s">
         <v>640</v>
       </c>
     </row>
@@ -10066,31 +10155,31 @@
       <c r="A162" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C162" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>895</v>
+        <v>12</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>912</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>896</v>
+        <v>913</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J162" t="s">
+      <c r="J162" s="1" t="s">
         <v>643</v>
       </c>
     </row>
@@ -10098,31 +10187,31 @@
       <c r="A163" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C163" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>895</v>
+        <v>12</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>914</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>897</v>
+        <v>915</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="J163" t="s">
+      <c r="J163" s="1" t="s">
         <v>646</v>
       </c>
     </row>
@@ -10145,7 +10234,7 @@
       <c r="F164" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="2" t="s">
         <v>648</v>
       </c>
       <c r="H164" s="1" t="s">
@@ -10154,7 +10243,7 @@
       <c r="I164" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="J164" t="s">
+      <c r="J164" s="1" t="s">
         <v>651</v>
       </c>
     </row>
@@ -10177,7 +10266,7 @@
       <c r="F165" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="G165" s="2" t="s">
         <v>653</v>
       </c>
       <c r="H165" s="1" t="s">
@@ -10186,7 +10275,7 @@
       <c r="I165" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="J165" t="s">
+      <c r="J165" s="1" t="s">
         <v>656</v>
       </c>
     </row>
@@ -10197,7 +10286,7 @@
       <c r="B166" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -10218,7 +10307,7 @@
       <c r="I166" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="J166" t="s">
+      <c r="J166" s="1" t="s">
         <v>661</v>
       </c>
     </row>
@@ -10226,10 +10315,10 @@
       <c r="A167" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -10238,7 +10327,7 @@
       <c r="E167" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F167" s="1" t="s">
         <v>218</v>
       </c>
       <c r="G167" s="2" t="s">
@@ -10250,7 +10339,7 @@
       <c r="I167" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="J167" t="s">
+      <c r="J167" s="1" t="s">
         <v>666</v>
       </c>
     </row>
@@ -10258,10 +10347,10 @@
       <c r="A168" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="1" t="s">
         <v>215</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -10270,7 +10359,7 @@
       <c r="E168" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F168" s="2" t="s">
+      <c r="F168" s="1" t="s">
         <v>328</v>
       </c>
       <c r="G168" s="2" t="s">
@@ -10282,7 +10371,7 @@
       <c r="I168" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="J168" t="s">
+      <c r="J168" s="1" t="s">
         <v>671</v>
       </c>
     </row>
@@ -10314,7 +10403,7 @@
       <c r="I169" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="J169" t="s">
+      <c r="J169" s="1" t="s">
         <v>692</v>
       </c>
     </row>
@@ -10346,7 +10435,7 @@
       <c r="I170" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="J170" t="s">
+      <c r="J170" s="1" t="s">
         <v>696</v>
       </c>
     </row>
@@ -10369,7 +10458,7 @@
       <c r="F171" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="G171" s="1" t="s">
+      <c r="G171" s="2" t="s">
         <v>697</v>
       </c>
       <c r="H171" s="1" t="s">
@@ -10378,7 +10467,7 @@
       <c r="I171" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="J171" t="s">
+      <c r="J171" s="1" t="s">
         <v>700</v>
       </c>
     </row>
@@ -10410,7 +10499,7 @@
       <c r="I172" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J172" s="1" t="s">
         <v>702</v>
       </c>
     </row>
@@ -10442,7 +10531,7 @@
       <c r="I173" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="J173" t="s">
+      <c r="J173" s="1" t="s">
         <v>704</v>
       </c>
     </row>
@@ -10474,7 +10563,7 @@
       <c r="I174" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="J174" t="s">
+      <c r="J174" s="1" t="s">
         <v>728</v>
       </c>
     </row>
@@ -10497,7 +10586,7 @@
       <c r="F175" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G175" s="2" t="s">
+      <c r="G175" s="1" t="s">
         <v>733</v>
       </c>
       <c r="H175" s="1" t="s">
@@ -10506,7 +10595,7 @@
       <c r="I175" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="J175" t="s">
+      <c r="J175" s="1" t="s">
         <v>732</v>
       </c>
     </row>
@@ -10538,7 +10627,7 @@
       <c r="I176" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="J176" t="s">
+      <c r="J176" s="1" t="s">
         <v>741</v>
       </c>
     </row>
@@ -10561,7 +10650,7 @@
       <c r="F177" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="G177" s="1" t="s">
         <v>745</v>
       </c>
       <c r="H177" s="1" t="s">
@@ -10570,7 +10659,7 @@
       <c r="I177" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="J177" t="s">
+      <c r="J177" s="1" t="s">
         <v>748</v>
       </c>
     </row>
@@ -10593,7 +10682,7 @@
       <c r="F178" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G178" s="2" t="s">
+      <c r="G178" s="1" t="s">
         <v>749</v>
       </c>
       <c r="H178" s="1" t="s">
@@ -10602,7 +10691,7 @@
       <c r="I178" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="J178" t="s">
+      <c r="J178" s="1" t="s">
         <v>752</v>
       </c>
     </row>
@@ -10639,34 +10728,34 @@
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180">
+      <c r="A180" s="1">
         <v>181</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B180" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F180" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G180" t="s">
+      <c r="G180" s="2" t="s">
         <v>758</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="I180" t="s">
+      <c r="I180" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="J180" t="s">
+      <c r="J180" s="1" t="s">
         <v>761</v>
       </c>
     </row>
@@ -10680,13 +10769,13 @@
       <c r="C181" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D181" s="1" t="s">
         <v>404</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F181" t="s">
+      <c r="F181" s="1" t="s">
         <v>404</v>
       </c>
       <c r="G181" s="2" t="s">
@@ -10698,7 +10787,7 @@
       <c r="I181" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="J181" t="s">
+      <c r="J181" s="1" t="s">
         <v>765</v>
       </c>
     </row>
@@ -10721,7 +10810,7 @@
       <c r="F182" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="G182" s="2" t="s">
         <v>771</v>
       </c>
       <c r="H182" s="1" t="s">
@@ -10753,7 +10842,7 @@
       <c r="F183" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="G183" s="1" t="s">
+      <c r="G183" s="2" t="s">
         <v>775</v>
       </c>
       <c r="H183" s="1" t="s">
@@ -10762,7 +10851,7 @@
       <c r="I183" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="J183" t="s">
+      <c r="J183" s="1" t="s">
         <v>777</v>
       </c>
     </row>
@@ -10794,7 +10883,7 @@
       <c r="I184" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="J184" t="s">
+      <c r="J184" s="1" t="s">
         <v>780</v>
       </c>
     </row>
@@ -10826,7 +10915,7 @@
       <c r="I185" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="J185" t="s">
+      <c r="J185" s="1" t="s">
         <v>784</v>
       </c>
     </row>
@@ -10849,7 +10938,7 @@
       <c r="F186" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="G186" s="1" t="s">
         <v>787</v>
       </c>
       <c r="H186" s="1" t="s">
@@ -10858,7 +10947,7 @@
       <c r="I186" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="J186" t="s">
+      <c r="J186" s="1" t="s">
         <v>790</v>
       </c>
     </row>
@@ -10881,7 +10970,7 @@
       <c r="F187" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="G187" s="1" t="s">
         <v>791</v>
       </c>
       <c r="H187" s="1" t="s">
@@ -10890,7 +10979,7 @@
       <c r="I187" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="J187" t="s">
+      <c r="J187" s="1" t="s">
         <v>794</v>
       </c>
     </row>
@@ -10913,7 +11002,7 @@
       <c r="F188" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="1" t="s">
         <v>795</v>
       </c>
       <c r="H188" s="1" t="s">
@@ -10922,7 +11011,7 @@
       <c r="I188" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="J188" t="s">
+      <c r="J188" s="1" t="s">
         <v>798</v>
       </c>
     </row>
@@ -10945,7 +11034,7 @@
       <c r="F189" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="1" t="s">
         <v>802</v>
       </c>
       <c r="H189" s="1" t="s">
@@ -10954,7 +11043,7 @@
       <c r="I189" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="J189" t="s">
+      <c r="J189" s="1" t="s">
         <v>805</v>
       </c>
     </row>
@@ -10974,10 +11063,10 @@
       <c r="E190" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F190" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="G190" s="1" t="s">
         <v>806</v>
       </c>
       <c r="H190" s="1" t="s">
@@ -10986,7 +11075,7 @@
       <c r="I190" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="J190" t="s">
+      <c r="J190" s="1" t="s">
         <v>809</v>
       </c>
     </row>
@@ -11090,7 +11179,7 @@
       <c r="A194" s="1">
         <v>195</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B194" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C194" s="1" t="s">
@@ -11122,7 +11211,7 @@
       <c r="A195" s="1">
         <v>196</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B195" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C195" s="1" t="s">
@@ -11154,7 +11243,7 @@
       <c r="A196" s="1">
         <v>197</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B196" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C196" s="1" t="s">
@@ -11186,7 +11275,7 @@
       <c r="A197" s="1">
         <v>198</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B197" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C197" s="1" t="s">
@@ -11218,7 +11307,7 @@
       <c r="A198" s="1">
         <v>199</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B198" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C198" s="1" t="s">
@@ -11250,7 +11339,7 @@
       <c r="A199" s="1">
         <v>200</v>
       </c>
-      <c r="B199" t="s">
+      <c r="B199" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C199" s="1" t="s">
@@ -11282,7 +11371,7 @@
       <c r="A200" s="1">
         <v>201</v>
       </c>
-      <c r="B200" t="s">
+      <c r="B200" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C200" s="1" t="s">
@@ -11314,7 +11403,7 @@
       <c r="A201" s="1">
         <v>202</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B201" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C201" s="1" t="s">
@@ -11346,7 +11435,7 @@
       <c r="A202" s="1">
         <v>203</v>
       </c>
-      <c r="B202" t="s">
+      <c r="B202" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C202" s="1" t="s">
@@ -11361,7 +11450,7 @@
       <c r="F202" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G202" t="s">
+      <c r="G202" s="1" t="s">
         <v>856</v>
       </c>
       <c r="H202" s="1" t="s">
@@ -11378,7 +11467,7 @@
       <c r="A203" s="1">
         <v>204</v>
       </c>
-      <c r="B203" t="s">
+      <c r="B203" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C203" s="1" t="s">
@@ -11410,7 +11499,7 @@
       <c r="A204" s="1">
         <v>205</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B204" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C204" s="1" t="s">
@@ -11425,7 +11514,7 @@
       <c r="F204" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="G204" t="s">
+      <c r="G204" s="1" t="s">
         <v>866</v>
       </c>
       <c r="H204" s="1" t="s">
@@ -11442,7 +11531,7 @@
       <c r="A205" s="1">
         <v>206</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B205" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C205" s="1" t="s">
@@ -11474,7 +11563,7 @@
       <c r="A206" s="1">
         <v>207</v>
       </c>
-      <c r="B206" t="s">
+      <c r="B206" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C206" s="1" t="s">
@@ -11489,7 +11578,7 @@
       <c r="F206" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="G206" t="s">
+      <c r="G206" s="1" t="s">
         <v>876</v>
       </c>
       <c r="H206" s="1" t="s">
@@ -11506,7 +11595,7 @@
       <c r="A207" s="1">
         <v>208</v>
       </c>
-      <c r="B207" t="s">
+      <c r="B207" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C207" s="1" t="s">
@@ -11538,7 +11627,7 @@
       <c r="A208" s="1">
         <v>209</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B208" s="1" t="s">
         <v>888</v>
       </c>
       <c r="C208" s="1" t="s">
@@ -11553,7 +11642,7 @@
       <c r="F208" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="G208" t="s">
+      <c r="G208" s="1" t="s">
         <v>884</v>
       </c>
       <c r="H208" s="1" t="s">
@@ -11567,99 +11656,355 @@
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209">
+      <c r="A209" s="1">
         <v>210</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B209" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C209" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D209" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F209" t="s">
+      <c r="F209" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G209" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="H209" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="H209" t="s">
+      <c r="I209" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="I209" t="s">
+      <c r="J209" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="J209" t="s">
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>211</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210">
-        <v>211</v>
-      </c>
-      <c r="B210" t="s">
-        <v>315</v>
-      </c>
-      <c r="C210" t="s">
-        <v>316</v>
-      </c>
-      <c r="D210" t="s">
-        <v>514</v>
-      </c>
-      <c r="E210" t="s">
-        <v>515</v>
-      </c>
-      <c r="F210" t="s">
+      <c r="G210" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="H210" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="G210" t="s">
-        <v>902</v>
-      </c>
-      <c r="H210" t="s">
+      <c r="I210" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="I210" t="s">
+      <c r="J210" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="J210" t="s">
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>212</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>213</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211">
-        <v>212</v>
-      </c>
-      <c r="B211" t="s">
-        <v>434</v>
-      </c>
-      <c r="C211" t="s">
-        <v>435</v>
-      </c>
-      <c r="D211" t="s">
-        <v>622</v>
-      </c>
-      <c r="E211" t="s">
-        <v>623</v>
-      </c>
-      <c r="F211" t="s">
-        <v>907</v>
-      </c>
-      <c r="G211" t="s">
-        <v>909</v>
-      </c>
-      <c r="H211" t="s">
-        <v>910</v>
-      </c>
-      <c r="I211" t="s">
-        <v>911</v>
-      </c>
-      <c r="J211" t="s">
-        <v>912</v>
+      <c r="F212" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>214</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>215</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>216</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>217</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>218</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>219</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="I218" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>220</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>946</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F761318-E521-49CC-87CA-F2F96E070365}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0E4B56-2299-43F4-A628-C8B142D5F00E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="948">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -4627,13 +4627,16 @@
     <t>Ножиці для пластикових трубок</t>
   </si>
   <si>
-    <t>Набір знімачів для роз'єднання пневматичних трубок та з'єднувачів серії NEWLINE***</t>
-  </si>
-  <si>
-    <t>child3_small_220.jpg</t>
-  </si>
-  <si>
-    <t>child3_big_220.jpg</t>
+    <t>Гніздо кутове 90° швидкороз’ємного з’єднання систем подачі AdBlue/DEF зі штуцером типу «ялинка» (відповідає SAE J2044) без кільця</t>
+  </si>
+  <si>
+    <t>Гніздо пряме швидкороз’ємного з’єднання систем подачі AdBlue/DEF зі штуцером типу «ялинка» (відповідає SAE J2044) без кільця</t>
+  </si>
+  <si>
+    <t>Штуцер трійник редукційний з внутрішнім конусом 60° з усіх сторін для гідравлічних систем (під сфероконічне ущільнення)</t>
+  </si>
+  <si>
+    <t>Штуцер-трійник редукційний з внутрішнім конусом 60° з усіх сторін. Призначений для герметичного з’єднання зі сферичними ніпелями в гідравлічних системах. Бічний відвід має змінений діаметр проходу, що дозволяє підключати елементи іншого розміру без додаткових перехідників. Сфероконічне з’єднання забезпечує надійне металеве ущільнення без застосування додаткових ущільнювальних матеріалів. Особливості та властивості: 1. Матеріал — сталь з покриттям «білий цинк» (гальванічне цинкування). 2. Тип ущільнення — сфероконічне. 3. Розташування редукційного відводу — перпендикулярне.</t>
   </si>
 </sst>
 </file>
@@ -4670,11 +4673,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4990,7 +4996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J219"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -5091,7 +5097,7 @@
       <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5123,7 +5129,7 @@
       <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5155,7 +5161,7 @@
       <c r="I5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5187,7 +5193,7 @@
       <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5219,7 +5225,7 @@
       <c r="I7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5251,7 +5257,7 @@
       <c r="I8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5283,7 +5289,7 @@
       <c r="I9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5315,7 +5321,7 @@
       <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5347,7 +5353,7 @@
       <c r="I11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5379,7 +5385,7 @@
       <c r="I12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5411,7 +5417,7 @@
       <c r="I13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5443,7 +5449,7 @@
       <c r="I14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5475,7 +5481,7 @@
       <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5507,7 +5513,7 @@
       <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5539,7 +5545,7 @@
       <c r="I17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>76</v>
       </c>
     </row>
@@ -5571,7 +5577,7 @@
       <c r="I18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5603,7 +5609,7 @@
       <c r="I19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5635,7 +5641,7 @@
       <c r="I20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5667,7 +5673,7 @@
       <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>91</v>
       </c>
     </row>
@@ -5699,7 +5705,7 @@
       <c r="I22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5731,7 +5737,7 @@
       <c r="I23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>98</v>
       </c>
     </row>
@@ -5763,7 +5769,7 @@
       <c r="I24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5795,7 +5801,7 @@
       <c r="I25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5827,7 +5833,7 @@
       <c r="I26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5859,7 +5865,7 @@
       <c r="I27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5891,7 +5897,7 @@
       <c r="I28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5923,7 +5929,7 @@
       <c r="I29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5955,7 +5961,7 @@
       <c r="I30" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5987,7 +5993,7 @@
       <c r="I31" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>126</v>
       </c>
     </row>
@@ -6019,7 +6025,7 @@
       <c r="I32" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6051,7 +6057,7 @@
       <c r="I33" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>134</v>
       </c>
     </row>
@@ -6083,7 +6089,7 @@
       <c r="I34" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6115,7 +6121,7 @@
       <c r="I35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6147,7 +6153,7 @@
       <c r="I36" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6179,11 +6185,11 @@
       <c r="I37" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -6193,7 +6199,7 @@
       <c r="C38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -6211,7 +6217,7 @@
       <c r="I38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6243,7 +6249,7 @@
       <c r="I39" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6275,7 +6281,7 @@
       <c r="I40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J40" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6307,7 +6313,7 @@
       <c r="I41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" t="s">
         <v>176</v>
       </c>
     </row>
@@ -6339,7 +6345,7 @@
       <c r="I42" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>180</v>
       </c>
     </row>
@@ -6371,7 +6377,7 @@
       <c r="I43" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6403,7 +6409,7 @@
       <c r="I44" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="J44" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6435,7 +6441,7 @@
       <c r="I45" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="J45" t="s">
         <v>192</v>
       </c>
     </row>
@@ -6467,7 +6473,7 @@
       <c r="I46" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="J46" t="s">
         <v>196</v>
       </c>
     </row>
@@ -6499,7 +6505,7 @@
       <c r="I47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6531,7 +6537,7 @@
       <c r="I48" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6563,11 +6569,11 @@
       <c r="I49" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6577,7 +6583,7 @@
       <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -6595,11 +6601,11 @@
       <c r="I50" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -6609,7 +6615,7 @@
       <c r="C51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -6627,7 +6633,7 @@
       <c r="I51" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6659,7 +6665,7 @@
       <c r="I52" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6691,7 +6697,7 @@
       <c r="I53" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="J53" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6723,7 +6729,7 @@
       <c r="I54" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6755,7 +6761,7 @@
       <c r="I55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" t="s">
         <v>234</v>
       </c>
     </row>
@@ -6787,7 +6793,7 @@
       <c r="I56" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>238</v>
       </c>
     </row>
@@ -6819,7 +6825,7 @@
       <c r="I57" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6851,7 +6857,7 @@
       <c r="I58" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6883,7 +6889,7 @@
       <c r="I59" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6915,7 +6921,7 @@
       <c r="I60" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>255</v>
       </c>
     </row>
@@ -6947,7 +6953,7 @@
       <c r="I61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" t="s">
         <v>259</v>
       </c>
     </row>
@@ -6979,7 +6985,7 @@
       <c r="I62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7011,7 +7017,7 @@
       <c r="I63" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" t="s">
         <v>270</v>
       </c>
     </row>
@@ -7043,7 +7049,7 @@
       <c r="I64" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" t="s">
         <v>274</v>
       </c>
     </row>
@@ -7075,7 +7081,7 @@
       <c r="I65" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" t="s">
         <v>278</v>
       </c>
     </row>
@@ -7107,7 +7113,7 @@
       <c r="I66" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" t="s">
         <v>282</v>
       </c>
     </row>
@@ -7139,7 +7145,7 @@
       <c r="I67" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" t="s">
         <v>286</v>
       </c>
     </row>
@@ -7171,7 +7177,7 @@
       <c r="I68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" t="s">
         <v>290</v>
       </c>
     </row>
@@ -7203,7 +7209,7 @@
       <c r="I69" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" t="s">
         <v>294</v>
       </c>
     </row>
@@ -7235,7 +7241,7 @@
       <c r="I70" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" t="s">
         <v>298</v>
       </c>
     </row>
@@ -7267,7 +7273,7 @@
       <c r="I71" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" t="s">
         <v>302</v>
       </c>
     </row>
@@ -7299,7 +7305,7 @@
       <c r="I72" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7331,7 +7337,7 @@
       <c r="I73" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" t="s">
         <v>310</v>
       </c>
     </row>
@@ -7363,7 +7369,7 @@
       <c r="I74" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" t="s">
         <v>314</v>
       </c>
     </row>
@@ -7395,7 +7401,7 @@
       <c r="I75" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" t="s">
         <v>320</v>
       </c>
     </row>
@@ -7427,7 +7433,7 @@
       <c r="I76" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" t="s">
         <v>322</v>
       </c>
     </row>
@@ -7459,7 +7465,7 @@
       <c r="I77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" t="s">
         <v>325</v>
       </c>
     </row>
@@ -7491,7 +7497,7 @@
       <c r="I78" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" t="s">
         <v>327</v>
       </c>
     </row>
@@ -7523,7 +7529,7 @@
       <c r="I79" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" t="s">
         <v>333</v>
       </c>
     </row>
@@ -7555,7 +7561,7 @@
       <c r="I80" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" t="s">
         <v>336</v>
       </c>
     </row>
@@ -7587,7 +7593,7 @@
       <c r="I81" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" t="s">
         <v>340</v>
       </c>
     </row>
@@ -7619,7 +7625,7 @@
       <c r="I82" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7651,7 +7657,7 @@
       <c r="I83" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="J83" t="s">
         <v>348</v>
       </c>
     </row>
@@ -7683,7 +7689,7 @@
       <c r="I84" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" t="s">
         <v>352</v>
       </c>
     </row>
@@ -7715,7 +7721,7 @@
       <c r="I85" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" t="s">
         <v>356</v>
       </c>
     </row>
@@ -7747,7 +7753,7 @@
       <c r="I86" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" t="s">
         <v>359</v>
       </c>
     </row>
@@ -7779,7 +7785,7 @@
       <c r="I87" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" t="s">
         <v>363</v>
       </c>
     </row>
@@ -7811,7 +7817,7 @@
       <c r="I88" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="J88" t="s">
         <v>367</v>
       </c>
     </row>
@@ -7843,7 +7849,7 @@
       <c r="I89" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J89" s="1" t="s">
+      <c r="J89" t="s">
         <v>371</v>
       </c>
     </row>
@@ -7875,7 +7881,7 @@
       <c r="I90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="J90" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7907,7 +7913,7 @@
       <c r="I91" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="J91" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7939,7 +7945,7 @@
       <c r="I92" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J92" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7971,7 +7977,7 @@
       <c r="I93" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="J93" t="s">
         <v>387</v>
       </c>
     </row>
@@ -8003,7 +8009,7 @@
       <c r="I94" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="J94" t="s">
         <v>391</v>
       </c>
     </row>
@@ -8035,7 +8041,7 @@
       <c r="I95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="J95" s="1" t="s">
+      <c r="J95" t="s">
         <v>395</v>
       </c>
     </row>
@@ -8067,7 +8073,7 @@
       <c r="I96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="J96" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8099,7 +8105,7 @@
       <c r="I97" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="J97" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8131,7 +8137,7 @@
       <c r="I98" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="J98" t="s">
         <v>675</v>
       </c>
     </row>
@@ -8154,7 +8160,7 @@
       <c r="F99" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" t="s">
         <v>676</v>
       </c>
       <c r="H99" s="1" t="s">
@@ -8163,7 +8169,7 @@
       <c r="I99" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="J99" s="1" t="s">
+      <c r="J99" t="s">
         <v>679</v>
       </c>
     </row>
@@ -8195,7 +8201,7 @@
       <c r="I100" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="J100" s="1" t="s">
+      <c r="J100" t="s">
         <v>683</v>
       </c>
     </row>
@@ -8227,7 +8233,7 @@
       <c r="I101" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="J101" t="s">
         <v>686</v>
       </c>
     </row>
@@ -8259,7 +8265,7 @@
       <c r="I102" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" t="s">
         <v>409</v>
       </c>
     </row>
@@ -8291,7 +8297,7 @@
       <c r="I103" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="J103" t="s">
         <v>413</v>
       </c>
     </row>
@@ -8323,7 +8329,7 @@
       <c r="I104" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="J104" s="1" t="s">
+      <c r="J104" t="s">
         <v>417</v>
       </c>
     </row>
@@ -8355,7 +8361,7 @@
       <c r="I105" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="J105" t="s">
         <v>421</v>
       </c>
     </row>
@@ -8387,7 +8393,7 @@
       <c r="I106" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="J106" s="1" t="s">
+      <c r="J106" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8419,7 +8425,7 @@
       <c r="I107" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="J107" t="s">
         <v>429</v>
       </c>
     </row>
@@ -8451,7 +8457,7 @@
       <c r="I108" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J108" s="1" t="s">
+      <c r="J108" t="s">
         <v>433</v>
       </c>
     </row>
@@ -8483,7 +8489,7 @@
       <c r="I109" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="J109" s="1" t="s">
+      <c r="J109" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8515,7 +8521,7 @@
       <c r="I110" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J110" s="1" t="s">
+      <c r="J110" t="s">
         <v>445</v>
       </c>
     </row>
@@ -8547,7 +8553,7 @@
       <c r="I111" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="J111" t="s">
         <v>449</v>
       </c>
     </row>
@@ -8579,7 +8585,7 @@
       <c r="I112" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="J112" s="1" t="s">
+      <c r="J112" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8611,7 +8617,7 @@
       <c r="I113" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="J113" s="1" t="s">
+      <c r="J113" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8643,7 +8649,7 @@
       <c r="I114" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="J114" s="1" t="s">
+      <c r="J114" t="s">
         <v>461</v>
       </c>
     </row>
@@ -8675,7 +8681,7 @@
       <c r="I115" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="J115" s="1" t="s">
+      <c r="J115" t="s">
         <v>465</v>
       </c>
     </row>
@@ -8707,7 +8713,7 @@
       <c r="I116" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="J116" s="1" t="s">
+      <c r="J116" t="s">
         <v>469</v>
       </c>
     </row>
@@ -8739,7 +8745,7 @@
       <c r="I117" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J117" s="1" t="s">
+      <c r="J117" t="s">
         <v>473</v>
       </c>
     </row>
@@ -8771,7 +8777,7 @@
       <c r="I118" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="J118" s="1" t="s">
+      <c r="J118" t="s">
         <v>477</v>
       </c>
     </row>
@@ -8803,7 +8809,7 @@
       <c r="I119" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="J119" s="1" t="s">
+      <c r="J119" t="s">
         <v>481</v>
       </c>
     </row>
@@ -8827,15 +8833,15 @@
         <v>436</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>454</v>
+        <v>946</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>455</v>
+        <v>947</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J120" s="1" t="s">
+      <c r="J120" t="s">
         <v>483</v>
       </c>
     </row>
@@ -8867,7 +8873,7 @@
       <c r="I121" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="J121" s="1" t="s">
+      <c r="J121" t="s">
         <v>487</v>
       </c>
     </row>
@@ -8899,7 +8905,7 @@
       <c r="I122" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="J122" t="s">
         <v>491</v>
       </c>
     </row>
@@ -8931,7 +8937,7 @@
       <c r="I123" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J123" s="1" t="s">
+      <c r="J123" t="s">
         <v>495</v>
       </c>
     </row>
@@ -8963,7 +8969,7 @@
       <c r="I124" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="J124" s="1" t="s">
+      <c r="J124" t="s">
         <v>499</v>
       </c>
     </row>
@@ -8995,11 +9001,11 @@
       <c r="I125" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="J125" s="1" t="s">
+      <c r="J125" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>129</v>
       </c>
@@ -9009,7 +9015,7 @@
       <c r="C126" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E126" s="1" t="s">
@@ -9027,11 +9033,11 @@
       <c r="I126" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="J126" s="1" t="s">
+      <c r="J126" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>130</v>
       </c>
@@ -9041,7 +9047,7 @@
       <c r="C127" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E127" s="1" t="s">
@@ -9059,11 +9065,11 @@
       <c r="I127" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="J127" s="1" t="s">
+      <c r="J127" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>131</v>
       </c>
@@ -9073,7 +9079,7 @@
       <c r="C128" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E128" s="1" t="s">
@@ -9091,11 +9097,11 @@
       <c r="I128" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="J128" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>132</v>
       </c>
@@ -9105,7 +9111,7 @@
       <c r="C129" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -9123,11 +9129,11 @@
       <c r="I129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="J129" s="1" t="s">
+      <c r="J129" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>133</v>
       </c>
@@ -9137,7 +9143,7 @@
       <c r="C130" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E130" s="1" t="s">
@@ -9155,11 +9161,11 @@
       <c r="I130" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="J130" s="1" t="s">
+      <c r="J130" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>134</v>
       </c>
@@ -9169,7 +9175,7 @@
       <c r="C131" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E131" s="1" t="s">
@@ -9187,11 +9193,11 @@
       <c r="I131" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="J131" s="1" t="s">
+      <c r="J131" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>135</v>
       </c>
@@ -9201,7 +9207,7 @@
       <c r="C132" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E132" s="1" t="s">
@@ -9219,7 +9225,7 @@
       <c r="I132" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="J132" s="1" t="s">
+      <c r="J132" t="s">
         <v>534</v>
       </c>
     </row>
@@ -9251,7 +9257,7 @@
       <c r="I133" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="J133" s="1" t="s">
+      <c r="J133" t="s">
         <v>542</v>
       </c>
     </row>
@@ -9283,7 +9289,7 @@
       <c r="I134" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="J134" s="1" t="s">
+      <c r="J134" t="s">
         <v>545</v>
       </c>
     </row>
@@ -9315,7 +9321,7 @@
       <c r="I135" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="J135" s="1" t="s">
+      <c r="J135" t="s">
         <v>548</v>
       </c>
     </row>
@@ -9347,7 +9353,7 @@
       <c r="I136" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="J136" s="1" t="s">
+      <c r="J136" t="s">
         <v>552</v>
       </c>
     </row>
@@ -9379,7 +9385,7 @@
       <c r="I137" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J137" s="1" t="s">
+      <c r="J137" t="s">
         <v>556</v>
       </c>
     </row>
@@ -9411,7 +9417,7 @@
       <c r="I138" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="J138" s="1" t="s">
+      <c r="J138" t="s">
         <v>560</v>
       </c>
     </row>
@@ -9443,7 +9449,7 @@
       <c r="I139" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="J139" s="1" t="s">
+      <c r="J139" t="s">
         <v>564</v>
       </c>
     </row>
@@ -9475,7 +9481,7 @@
       <c r="I140" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J140" t="s">
         <v>567</v>
       </c>
     </row>
@@ -9507,7 +9513,7 @@
       <c r="I141" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="J141" s="1" t="s">
+      <c r="J141" t="s">
         <v>570</v>
       </c>
     </row>
@@ -9539,7 +9545,7 @@
       <c r="I142" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="J142" s="1" t="s">
+      <c r="J142" t="s">
         <v>574</v>
       </c>
     </row>
@@ -9571,7 +9577,7 @@
       <c r="I143" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="J143" s="1" t="s">
+      <c r="J143" t="s">
         <v>577</v>
       </c>
     </row>
@@ -9603,7 +9609,7 @@
       <c r="I144" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="J144" s="1" t="s">
+      <c r="J144" t="s">
         <v>581</v>
       </c>
     </row>
@@ -9635,7 +9641,7 @@
       <c r="I145" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="J145" s="1" t="s">
+      <c r="J145" t="s">
         <v>583</v>
       </c>
     </row>
@@ -9667,7 +9673,7 @@
       <c r="I146" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="J146" t="s">
         <v>587</v>
       </c>
     </row>
@@ -9699,7 +9705,7 @@
       <c r="I147" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="J147" t="s">
         <v>589</v>
       </c>
     </row>
@@ -9731,7 +9737,7 @@
       <c r="I148" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="J148" t="s">
         <v>591</v>
       </c>
     </row>
@@ -9763,7 +9769,7 @@
       <c r="I149" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="J149" t="s">
         <v>593</v>
       </c>
     </row>
@@ -9795,7 +9801,7 @@
       <c r="I150" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="J150" s="1" t="s">
+      <c r="J150" t="s">
         <v>597</v>
       </c>
     </row>
@@ -9827,7 +9833,7 @@
       <c r="I151" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="J151" s="1" t="s">
+      <c r="J151" t="s">
         <v>601</v>
       </c>
     </row>
@@ -9859,7 +9865,7 @@
       <c r="I152" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="J152" t="s">
         <v>605</v>
       </c>
     </row>
@@ -9891,7 +9897,7 @@
       <c r="I153" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="J153" s="1" t="s">
+      <c r="J153" t="s">
         <v>609</v>
       </c>
     </row>
@@ -9923,7 +9929,7 @@
       <c r="I154" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="J154" s="1" t="s">
+      <c r="J154" t="s">
         <v>613</v>
       </c>
     </row>
@@ -9955,7 +9961,7 @@
       <c r="I155" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="J155" s="1" t="s">
+      <c r="J155" t="s">
         <v>617</v>
       </c>
     </row>
@@ -9987,7 +9993,7 @@
       <c r="I156" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="J156" s="1" t="s">
+      <c r="J156" t="s">
         <v>621</v>
       </c>
     </row>
@@ -10019,7 +10025,7 @@
       <c r="I157" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="J157" s="1" t="s">
+      <c r="J157" t="s">
         <v>626</v>
       </c>
     </row>
@@ -10051,7 +10057,7 @@
       <c r="I158" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="J158" s="1" t="s">
+      <c r="J158" t="s">
         <v>629</v>
       </c>
     </row>
@@ -10083,7 +10089,7 @@
       <c r="I159" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="J159" s="1" t="s">
+      <c r="J159" t="s">
         <v>632</v>
       </c>
     </row>
@@ -10115,7 +10121,7 @@
       <c r="I160" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="J160" s="1" t="s">
+      <c r="J160" t="s">
         <v>635</v>
       </c>
     </row>
@@ -10147,7 +10153,7 @@
       <c r="I161" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="J161" s="1" t="s">
+      <c r="J161" t="s">
         <v>640</v>
       </c>
     </row>
@@ -10179,7 +10185,7 @@
       <c r="I162" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="J162" t="s">
         <v>643</v>
       </c>
     </row>
@@ -10211,7 +10217,7 @@
       <c r="I163" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="J163" s="1" t="s">
+      <c r="J163" t="s">
         <v>646</v>
       </c>
     </row>
@@ -10243,7 +10249,7 @@
       <c r="I164" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="J164" s="1" t="s">
+      <c r="J164" t="s">
         <v>651</v>
       </c>
     </row>
@@ -10275,7 +10281,7 @@
       <c r="I165" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="J165" s="1" t="s">
+      <c r="J165" t="s">
         <v>656</v>
       </c>
     </row>
@@ -10307,7 +10313,7 @@
       <c r="I166" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="J166" s="1" t="s">
+      <c r="J166" t="s">
         <v>661</v>
       </c>
     </row>
@@ -10339,7 +10345,7 @@
       <c r="I167" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="J167" s="1" t="s">
+      <c r="J167" t="s">
         <v>666</v>
       </c>
     </row>
@@ -10371,7 +10377,7 @@
       <c r="I168" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="J168" s="1" t="s">
+      <c r="J168" t="s">
         <v>671</v>
       </c>
     </row>
@@ -10403,7 +10409,7 @@
       <c r="I169" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="J169" s="1" t="s">
+      <c r="J169" t="s">
         <v>692</v>
       </c>
     </row>
@@ -10435,7 +10441,7 @@
       <c r="I170" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="J170" s="1" t="s">
+      <c r="J170" t="s">
         <v>696</v>
       </c>
     </row>
@@ -10467,7 +10473,7 @@
       <c r="I171" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="J171" s="1" t="s">
+      <c r="J171" t="s">
         <v>700</v>
       </c>
     </row>
@@ -10491,7 +10497,7 @@
         <v>688</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>697</v>
+        <v>944</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>698</v>
@@ -10499,7 +10505,7 @@
       <c r="I172" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="J172" s="1" t="s">
+      <c r="J172" t="s">
         <v>702</v>
       </c>
     </row>
@@ -10523,7 +10529,7 @@
         <v>688</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>689</v>
+        <v>945</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>690</v>
@@ -10531,11 +10537,11 @@
       <c r="I173" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="J173" s="1" t="s">
+      <c r="J173" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>175</v>
       </c>
@@ -10545,7 +10551,7 @@
       <c r="C174" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="D174" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E174" s="1" t="s">
@@ -10568,38 +10574,38 @@
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="1">
+      <c r="A175">
         <v>176</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B175" t="s">
         <v>214</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="C175" t="s">
         <v>215</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="D175" t="s">
         <v>216</v>
       </c>
-      <c r="E175" s="1" t="s">
+      <c r="E175" t="s">
         <v>217</v>
       </c>
-      <c r="F175" s="1" t="s">
+      <c r="F175" t="s">
         <v>218</v>
       </c>
-      <c r="G175" s="1" t="s">
+      <c r="G175" t="s">
         <v>733</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="I175" s="1" t="s">
+      <c r="I175" t="s">
         <v>731</v>
       </c>
-      <c r="J175" s="1" t="s">
+      <c r="J175" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>177</v>
       </c>
@@ -10609,13 +10615,13 @@
       <c r="C176" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="D176" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F176" s="1" t="s">
+      <c r="F176" t="s">
         <v>157</v>
       </c>
       <c r="G176" s="2" t="s">
@@ -10627,11 +10633,11 @@
       <c r="I176" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="J176" s="1" t="s">
+      <c r="J176" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>178</v>
       </c>
@@ -10641,7 +10647,7 @@
       <c r="C177" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="D177" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E177" s="1" t="s">
@@ -10691,7 +10697,7 @@
       <c r="I178" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="J178" s="1" t="s">
+      <c r="J178" t="s">
         <v>752</v>
       </c>
     </row>
@@ -10723,7 +10729,7 @@
       <c r="I179" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="J179" s="1" t="s">
+      <c r="J179" t="s">
         <v>757</v>
       </c>
     </row>
@@ -10755,7 +10761,7 @@
       <c r="I180" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="J180" s="1" t="s">
+      <c r="J180" t="s">
         <v>761</v>
       </c>
     </row>
@@ -10787,7 +10793,7 @@
       <c r="I181" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="J181" s="1" t="s">
+      <c r="J181" t="s">
         <v>765</v>
       </c>
     </row>
@@ -10819,7 +10825,7 @@
       <c r="I182" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="J182" s="1" t="s">
+      <c r="J182" t="s">
         <v>774</v>
       </c>
     </row>
@@ -10851,7 +10857,7 @@
       <c r="I183" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="J183" s="1" t="s">
+      <c r="J183" t="s">
         <v>777</v>
       </c>
     </row>
@@ -10883,7 +10889,7 @@
       <c r="I184" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="J184" s="1" t="s">
+      <c r="J184" t="s">
         <v>780</v>
       </c>
     </row>
@@ -10903,7 +10909,7 @@
       <c r="E185" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="F185" s="1" t="s">
+      <c r="F185" t="s">
         <v>781</v>
       </c>
       <c r="G185" s="2" t="s">
@@ -10915,7 +10921,7 @@
       <c r="I185" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="J185" s="1" t="s">
+      <c r="J185" t="s">
         <v>784</v>
       </c>
     </row>
@@ -10923,7 +10929,7 @@
       <c r="A186" s="1">
         <v>187</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" t="s">
         <v>888</v>
       </c>
       <c r="C186" s="1" t="s">
@@ -10955,7 +10961,7 @@
       <c r="A187" s="1">
         <v>188</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B187" t="s">
         <v>888</v>
       </c>
       <c r="C187" s="1" t="s">
@@ -10987,7 +10993,7 @@
       <c r="A188" s="1">
         <v>189</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B188" t="s">
         <v>888</v>
       </c>
       <c r="C188" s="1" t="s">
@@ -11019,7 +11025,7 @@
       <c r="A189" s="1">
         <v>190</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B189" t="s">
         <v>888</v>
       </c>
       <c r="C189" s="1" t="s">
@@ -11051,7 +11057,7 @@
       <c r="A190" s="1">
         <v>191</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B190" t="s">
         <v>888</v>
       </c>
       <c r="C190" s="1" t="s">
@@ -11083,7 +11089,7 @@
       <c r="A191" s="1">
         <v>192</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B191" t="s">
         <v>888</v>
       </c>
       <c r="C191" s="1" t="s">
@@ -11115,7 +11121,7 @@
       <c r="A192" s="1">
         <v>193</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" t="s">
         <v>888</v>
       </c>
       <c r="C192" s="1" t="s">
@@ -11147,7 +11153,7 @@
       <c r="A193" s="1">
         <v>194</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B193" t="s">
         <v>888</v>
       </c>
       <c r="C193" s="1" t="s">
@@ -11179,7 +11185,7 @@
       <c r="A194" s="1">
         <v>195</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" t="s">
         <v>888</v>
       </c>
       <c r="C194" s="1" t="s">
@@ -11211,7 +11217,7 @@
       <c r="A195" s="1">
         <v>196</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" t="s">
         <v>888</v>
       </c>
       <c r="C195" s="1" t="s">
@@ -11243,7 +11249,7 @@
       <c r="A196" s="1">
         <v>197</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B196" t="s">
         <v>888</v>
       </c>
       <c r="C196" s="1" t="s">
@@ -11275,7 +11281,7 @@
       <c r="A197" s="1">
         <v>198</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="B197" t="s">
         <v>888</v>
       </c>
       <c r="C197" s="1" t="s">
@@ -11290,7 +11296,7 @@
       <c r="F197" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G197" s="1" t="s">
+      <c r="G197" t="s">
         <v>834</v>
       </c>
       <c r="H197" s="1" t="s">
@@ -11307,7 +11313,7 @@
       <c r="A198" s="1">
         <v>199</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B198" t="s">
         <v>888</v>
       </c>
       <c r="C198" s="1" t="s">
@@ -11339,7 +11345,7 @@
       <c r="A199" s="1">
         <v>200</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="B199" t="s">
         <v>888</v>
       </c>
       <c r="C199" s="1" t="s">
@@ -11354,7 +11360,7 @@
       <c r="F199" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" t="s">
         <v>842</v>
       </c>
       <c r="H199" s="1" t="s">
@@ -11371,7 +11377,7 @@
       <c r="A200" s="1">
         <v>201</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" t="s">
         <v>888</v>
       </c>
       <c r="C200" s="1" t="s">
@@ -11403,7 +11409,7 @@
       <c r="A201" s="1">
         <v>202</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B201" t="s">
         <v>888</v>
       </c>
       <c r="C201" s="1" t="s">
@@ -11418,7 +11424,7 @@
       <c r="F201" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="G201" s="1" t="s">
+      <c r="G201" t="s">
         <v>852</v>
       </c>
       <c r="H201" s="1" t="s">
@@ -11435,7 +11441,7 @@
       <c r="A202" s="1">
         <v>203</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="B202" t="s">
         <v>888</v>
       </c>
       <c r="C202" s="1" t="s">
@@ -11467,7 +11473,7 @@
       <c r="A203" s="1">
         <v>204</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B203" t="s">
         <v>888</v>
       </c>
       <c r="C203" s="1" t="s">
@@ -11482,7 +11488,7 @@
       <c r="F203" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="G203" s="1" t="s">
+      <c r="G203" t="s">
         <v>862</v>
       </c>
       <c r="H203" s="1" t="s">
@@ -11499,7 +11505,7 @@
       <c r="A204" s="1">
         <v>205</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="B204" t="s">
         <v>888</v>
       </c>
       <c r="C204" s="1" t="s">
@@ -11531,7 +11537,7 @@
       <c r="A205" s="1">
         <v>206</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="B205" t="s">
         <v>888</v>
       </c>
       <c r="C205" s="1" t="s">
@@ -11546,10 +11552,10 @@
       <c r="F205" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="G205" s="1" t="s">
+      <c r="G205" t="s">
         <v>873</v>
       </c>
-      <c r="H205" s="1" t="s">
+      <c r="H205" t="s">
         <v>873</v>
       </c>
       <c r="I205" s="1" t="s">
@@ -11563,7 +11569,7 @@
       <c r="A206" s="1">
         <v>207</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="B206" t="s">
         <v>888</v>
       </c>
       <c r="C206" s="1" t="s">
@@ -11595,7 +11601,7 @@
       <c r="A207" s="1">
         <v>208</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="B207" t="s">
         <v>888</v>
       </c>
       <c r="C207" s="1" t="s">
@@ -11627,25 +11633,25 @@
       <c r="A208" s="1">
         <v>209</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="B208" t="s">
         <v>888</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D208" t="s">
         <v>884</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="F208" s="1" t="s">
+      <c r="F208" t="s">
         <v>884</v>
       </c>
-      <c r="G208" s="1" t="s">
+      <c r="G208" t="s">
         <v>884</v>
       </c>
-      <c r="H208" s="1" t="s">
+      <c r="H208" t="s">
         <v>884</v>
       </c>
       <c r="I208" s="1" t="s">
@@ -11656,7 +11662,7 @@
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="1">
+      <c r="A209">
         <v>210</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -11680,14 +11686,14 @@
       <c r="H209" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="I209" s="1" t="s">
+      <c r="I209" t="s">
         <v>899</v>
       </c>
-      <c r="J209" s="1" t="s">
+      <c r="J209" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>211</v>
       </c>
@@ -11697,7 +11703,7 @@
       <c r="C210" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D210" s="3" t="s">
         <v>514</v>
       </c>
       <c r="E210" s="1" t="s">
@@ -11738,7 +11744,7 @@
       <c r="F211" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="G211" s="1" t="s">
+      <c r="G211" t="s">
         <v>908</v>
       </c>
       <c r="H211" s="1" t="s">
@@ -11747,12 +11753,12 @@
       <c r="I211" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="J211" s="1" t="s">
+      <c r="J211" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="1">
+      <c r="A212">
         <v>213</v>
       </c>
       <c r="B212" s="2" t="s">
@@ -11779,12 +11785,12 @@
       <c r="I212" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="J212" s="1" t="s">
+      <c r="J212" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="1">
+      <c r="A213">
         <v>214</v>
       </c>
       <c r="B213" s="2" t="s">
@@ -11802,7 +11808,7 @@
       <c r="F213" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="G213" s="1" t="s">
+      <c r="G213" t="s">
         <v>920</v>
       </c>
       <c r="H213" s="1" t="s">
@@ -11811,12 +11817,12 @@
       <c r="I213" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="J213" s="1" t="s">
+      <c r="J213" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" s="1">
+      <c r="A214">
         <v>215</v>
       </c>
       <c r="B214" s="2" t="s">
@@ -11831,10 +11837,10 @@
       <c r="E214" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F214" t="s">
         <v>924</v>
       </c>
-      <c r="G214" s="1" t="s">
+      <c r="G214" t="s">
         <v>924</v>
       </c>
       <c r="H214" s="1" t="s">
@@ -11843,12 +11849,12 @@
       <c r="I214" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="J214" s="1" t="s">
+      <c r="J214" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="1">
+      <c r="A215">
         <v>216</v>
       </c>
       <c r="B215" s="2" t="s">
@@ -11863,10 +11869,10 @@
       <c r="E215" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="F215" s="1" t="s">
+      <c r="F215" t="s">
         <v>942</v>
       </c>
-      <c r="G215" s="1" t="s">
+      <c r="G215" t="s">
         <v>928</v>
       </c>
       <c r="H215" s="1" t="s">
@@ -11875,12 +11881,12 @@
       <c r="I215" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="J215" s="1" t="s">
+      <c r="J215" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="1">
+      <c r="A216">
         <v>217</v>
       </c>
       <c r="B216" s="2" t="s">
@@ -11895,10 +11901,10 @@
       <c r="E216" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="F216" s="1" t="s">
+      <c r="F216" t="s">
         <v>942</v>
       </c>
-      <c r="G216" s="1" t="s">
+      <c r="G216" t="s">
         <v>932</v>
       </c>
       <c r="H216" s="1" t="s">
@@ -11907,12 +11913,12 @@
       <c r="I216" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="J216" s="1" t="s">
+      <c r="J216" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="1">
+      <c r="A217">
         <v>218</v>
       </c>
       <c r="B217" s="2" t="s">
@@ -11939,12 +11945,12 @@
       <c r="I217" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="J217" s="1" t="s">
+      <c r="J217" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" s="1">
+      <c r="A218">
         <v>219</v>
       </c>
       <c r="B218" s="2" t="s">
@@ -11971,40 +11977,8 @@
       <c r="I218" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="J218" s="1" t="s">
+      <c r="J218" t="s">
         <v>941</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" s="1">
-        <v>220</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>918</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>942</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="H219" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="I219" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>946</v>
       </c>
     </row>
   </sheetData>

--- a/source/connector_tree.xlsx
+++ b/source/connector_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4288C3DF-DFAA-4CE5-ABE1-0D5C60A1337C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FF9859-7544-4808-9248-FD06766B3663}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{0D852C87-3D23-457A-9A5F-D58A23A72E0B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="968">
   <si>
     <t>Номер группы ch3</t>
   </si>
@@ -4648,6 +4648,63 @@
   </si>
   <si>
     <t>child3_big_220.jpg</t>
+  </si>
+  <si>
+    <t>Захисні чохли та пробки для гідравлічних швидкороз'ємних з'єднань</t>
+  </si>
+  <si>
+    <t>child1_33.jpg</t>
+  </si>
+  <si>
+    <t>Захисні чохли для ніпелів гідравлічних швидкороз'ємних з'єднань</t>
+  </si>
+  <si>
+    <t>Захисні чохли для ніпелів гідравлічних швидкороз'ємних з'єднань
+ Призначення: Герметичний захист робочої зони ніпеля від пилу, абразивних частинок та вологи.
+Наявність фіксувального кільця (ремінця): Призначене для надійного утримання чохла на корпусі ШРЗ, що повністю запобігає його втраті під час роботи гідросистеми.
+Матеріал: Високоякісний еластичний полімер, стійкий до мастил, палива та перепадів температур.</t>
+  </si>
+  <si>
+    <t>child3_small_221.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_221.jpg</t>
+  </si>
+  <si>
+    <t>Захисні пробки для розеток гідравлічних швидкороз'ємних з'єднань</t>
+  </si>
+  <si>
+    <t>Захисні пробки для розеток гідравлічних швидкороз'ємних з'єднань
+Призначення: Герметичний захист внутрішньої порожнини розетки (муфти «мама») від потрапляння пилу, бруду, води та сторонніх частинок у роз'єднаному стані
+Наявність фіксувального кільця (ремінця): Призначене для надійного утримання пробки на корпусі ШРЗ, що повністю запобігає її втраті під час роботи гідросистеми
+Матеріал: Високоякісний еластичний полімер, стійкий до мастил, палива та перепадів температур</t>
+  </si>
+  <si>
+    <t>child3_small_222.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_222.jpg</t>
+  </si>
+  <si>
+    <t>Зворотні клапани паливної системи</t>
+  </si>
+  <si>
+    <t>Зворотні клапани паливної системи
+Паливні зворотні клапани встановлюються безпосередньо в паливопровідну магістраль транспортних засобів. Вони забезпечують рух палива суворо в одному напрямку та ефективно запобігають спустошенню паливопроводів (відтоку палива назад у бак) після зупинки двигуна. Це гарантує швидкий та стабільний запуск системи за будь-яких умов.
+• Висока універсальність: Зворотні клапани розраховані на тривалу роботу з усіма стандартними видами моторного палива, що відповідають нормам безпеки.
+• Надійний матеріал: Корпус виконаний з міцного алюмінію, стійкого до корозії, агресивного хімічного середовища та температурних перепадів.
+• Просте встановлення: На корпус деталі нанесено чітку стрілку, яка вказує точний напрямок потоку палива, що виключає помилки під час монтажу.
+Технічні характеристики:
+• Довжина: 60 мм
+• Ширина зіва гайкового ключа (HEX): 20 мм
+• Матеріал корпусу: Алюміній
+• Робоче середовище: Всі стандартні види автомобільного палива (бензин, дизель)</t>
+  </si>
+  <si>
+    <t>child3_small_223.jpg</t>
+  </si>
+  <si>
+    <t>child3_big_223.jpg</t>
   </si>
 </sst>
 </file>
@@ -5004,7 +5061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E981325-28A9-4E59-A5CD-40BEADDC6A98}">
-  <dimension ref="A1:J219"/>
+  <dimension ref="A1:J222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
@@ -12021,6 +12078,102 @@
         <v>911</v>
       </c>
     </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>221</v>
+      </c>
+      <c r="B220" t="s">
+        <v>938</v>
+      </c>
+      <c r="C220" t="s">
+        <v>414</v>
+      </c>
+      <c r="D220" t="s">
+        <v>954</v>
+      </c>
+      <c r="E220" t="s">
+        <v>955</v>
+      </c>
+      <c r="F220" t="s">
+        <v>956</v>
+      </c>
+      <c r="G220" t="s">
+        <v>956</v>
+      </c>
+      <c r="H220" t="s">
+        <v>957</v>
+      </c>
+      <c r="I220" t="s">
+        <v>958</v>
+      </c>
+      <c r="J220" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>222</v>
+      </c>
+      <c r="B221" t="s">
+        <v>938</v>
+      </c>
+      <c r="C221" t="s">
+        <v>414</v>
+      </c>
+      <c r="D221" t="s">
+        <v>954</v>
+      </c>
+      <c r="E221" t="s">
+        <v>955</v>
+      </c>
+      <c r="F221" t="s">
+        <v>960</v>
+      </c>
+      <c r="G221" t="s">
+        <v>960</v>
+      </c>
+      <c r="H221" t="s">
+        <v>961</v>
+      </c>
+      <c r="I221" t="s">
+        <v>962</v>
+      </c>
+      <c r="J221" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>223</v>
+      </c>
+      <c r="B222" t="s">
+        <v>930</v>
+      </c>
+      <c r="C222" t="s">
+        <v>303</v>
+      </c>
+      <c r="D222" t="s">
+        <v>490</v>
+      </c>
+      <c r="E222" t="s">
+        <v>491</v>
+      </c>
+      <c r="F222" t="s">
+        <v>964</v>
+      </c>
+      <c r="G222" t="s">
+        <v>964</v>
+      </c>
+      <c r="H222" t="s">
+        <v>965</v>
+      </c>
+      <c r="I222" t="s">
+        <v>966</v>
+      </c>
+      <c r="J222" t="s">
+        <v>967</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J182" xr:uid="{7FC527DB-17BF-453D-BE91-6A17C45BA147}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
